--- a/data/ei/Data_modeller.xlsx
+++ b/data/ei/Data_modeller.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q149"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,62 +469,27 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Avskrivning</t>
+          <t>CU</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Avkastning</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>CU</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>MWhl</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>MWhl</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
           <t>MWhh</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Avkastning_2024</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Avkastning_2025</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Avkastning_2026</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Avkastning_2027</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Avkastning_Period</t>
         </is>
       </c>
     </row>
@@ -549,40 +514,19 @@
         <v>59620.58022504699</v>
       </c>
       <c r="F2" t="n">
-        <v>31020.0820997732</v>
+        <v>13330.5</v>
       </c>
       <c r="G2" t="n">
-        <v>28600.49812527379</v>
+        <v>54.95</v>
       </c>
       <c r="H2" t="n">
-        <v>13330.5</v>
+        <v>394.5</v>
       </c>
       <c r="I2" t="n">
-        <v>54.95</v>
+        <v>183522.25</v>
       </c>
       <c r="J2" t="n">
-        <v>394.5</v>
-      </c>
-      <c r="K2" t="n">
-        <v>183522.25</v>
-      </c>
-      <c r="L2" t="n">
         <v>21546</v>
-      </c>
-      <c r="M2" t="n">
-        <v>28600.5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>28280.060546875</v>
-      </c>
-      <c r="O2" t="n">
-        <v>27967.349609375</v>
-      </c>
-      <c r="P2" t="n">
-        <v>27648.869140625</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>112496.779296875</v>
       </c>
     </row>
     <row r="3">
@@ -606,40 +550,19 @@
         <v>1635.926714697056</v>
       </c>
       <c r="F3" t="n">
-        <v>916.7599550874646</v>
+        <v>315.75</v>
       </c>
       <c r="G3" t="n">
-        <v>719.1667596095912</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>315.75</v>
+        <v>41.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>4871</v>
       </c>
       <c r="J3" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4871</v>
-      </c>
-      <c r="L3" t="n">
         <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>719.1699829101562</v>
-      </c>
-      <c r="N3" t="n">
-        <v>725.4199829101562</v>
-      </c>
-      <c r="O3" t="n">
-        <v>694.969970703125</v>
-      </c>
-      <c r="P3" t="n">
-        <v>717.9600219726562</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2857.519958496094</v>
       </c>
     </row>
     <row r="4">
@@ -663,40 +586,19 @@
         <v>27479.54148800415</v>
       </c>
       <c r="F4" t="n">
-        <v>15255.024903015</v>
+        <v>5027</v>
       </c>
       <c r="G4" t="n">
-        <v>12224.51658498916</v>
+        <v>32.25</v>
       </c>
       <c r="H4" t="n">
-        <v>5027</v>
+        <v>145.25</v>
       </c>
       <c r="I4" t="n">
-        <v>32.25</v>
+        <v>73611.75</v>
       </c>
       <c r="J4" t="n">
-        <v>145.25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>73611.75</v>
-      </c>
-      <c r="L4" t="n">
         <v>54887.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>12224.51953125</v>
-      </c>
-      <c r="N4" t="n">
-        <v>12184.740234375</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12005.2099609375</v>
-      </c>
-      <c r="P4" t="n">
-        <v>11715.8203125</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>48130.2900390625</v>
       </c>
     </row>
     <row r="5">
@@ -720,40 +622,19 @@
         <v>40359.33384022739</v>
       </c>
       <c r="F5" t="n">
-        <v>19943.4312792123</v>
+        <v>10309.75</v>
       </c>
       <c r="G5" t="n">
-        <v>20415.90256101508</v>
+        <v>39.5</v>
       </c>
       <c r="H5" t="n">
-        <v>10309.75</v>
+        <v>216.25</v>
       </c>
       <c r="I5" t="n">
-        <v>39.5</v>
+        <v>118689.75</v>
       </c>
       <c r="J5" t="n">
-        <v>216.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>118689.75</v>
-      </c>
-      <c r="L5" t="n">
         <v>31668.25</v>
-      </c>
-      <c r="M5" t="n">
-        <v>20415.900390625</v>
-      </c>
-      <c r="N5" t="n">
-        <v>20173.23046875</v>
-      </c>
-      <c r="O5" t="n">
-        <v>19835.30078125</v>
-      </c>
-      <c r="P5" t="n">
-        <v>19570.130859375</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>79994.5625</v>
       </c>
     </row>
     <row r="6">
@@ -777,40 +658,19 @@
         <v>9354.045726833258</v>
       </c>
       <c r="F6" t="n">
-        <v>5451.25911899054</v>
+        <v>2351.75</v>
       </c>
       <c r="G6" t="n">
-        <v>3902.786607842717</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
-        <v>2351.75</v>
+        <v>56</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>29847.75</v>
       </c>
       <c r="J6" t="n">
-        <v>56</v>
-      </c>
-      <c r="K6" t="n">
-        <v>29847.75</v>
-      </c>
-      <c r="L6" t="n">
         <v>621.25</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3902.7900390625</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3730.760009765625</v>
-      </c>
-      <c r="O6" t="n">
-        <v>3554.31005859375</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3371.929931640625</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>14559.7900390625</v>
       </c>
     </row>
     <row r="7">
@@ -834,40 +694,19 @@
         <v>70422.21921883929</v>
       </c>
       <c r="F7" t="n">
-        <v>33950.712000622</v>
+        <v>8041.75</v>
       </c>
       <c r="G7" t="n">
-        <v>36471.5072182173</v>
+        <v>95.4375</v>
       </c>
       <c r="H7" t="n">
-        <v>8041.75</v>
+        <v>493.5</v>
       </c>
       <c r="I7" t="n">
-        <v>95.4375</v>
+        <v>129882.75</v>
       </c>
       <c r="J7" t="n">
-        <v>493.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>129882.75</v>
-      </c>
-      <c r="L7" t="n">
         <v>10286.75</v>
-      </c>
-      <c r="M7" t="n">
-        <v>36471.51171875</v>
-      </c>
-      <c r="N7" t="n">
-        <v>38894.578125</v>
-      </c>
-      <c r="O7" t="n">
-        <v>39703.87109375</v>
-      </c>
-      <c r="P7" t="n">
-        <v>41271.921875</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>156341.8828125</v>
       </c>
     </row>
     <row r="8">
@@ -891,40 +730,19 @@
         <v>65761.46440754113</v>
       </c>
       <c r="F8" t="n">
-        <v>35981.15170650333</v>
+        <v>13821</v>
       </c>
       <c r="G8" t="n">
-        <v>29780.3127010378</v>
+        <v>64.235</v>
       </c>
       <c r="H8" t="n">
-        <v>13821</v>
+        <v>382.75</v>
       </c>
       <c r="I8" t="n">
-        <v>64.235</v>
+        <v>188168</v>
       </c>
       <c r="J8" t="n">
-        <v>382.75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>188168</v>
-      </c>
-      <c r="L8" t="n">
         <v>31165</v>
-      </c>
-      <c r="M8" t="n">
-        <v>29780.310546875</v>
-      </c>
-      <c r="N8" t="n">
-        <v>29697.029296875</v>
-      </c>
-      <c r="O8" t="n">
-        <v>29533.140625</v>
-      </c>
-      <c r="P8" t="n">
-        <v>29258.640625</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>118269.12109375</v>
       </c>
     </row>
     <row r="9">
@@ -948,40 +766,19 @@
         <v>35099.06099737207</v>
       </c>
       <c r="F9" t="n">
-        <v>16729.32290036678</v>
+        <v>4945</v>
       </c>
       <c r="G9" t="n">
-        <v>18369.73809700529</v>
+        <v>21.55</v>
       </c>
       <c r="H9" t="n">
-        <v>4945</v>
+        <v>358.5</v>
       </c>
       <c r="I9" t="n">
-        <v>21.55</v>
+        <v>72008.25</v>
       </c>
       <c r="J9" t="n">
-        <v>358.5</v>
-      </c>
-      <c r="K9" t="n">
-        <v>72008.25</v>
-      </c>
-      <c r="L9" t="n">
         <v>1853</v>
-      </c>
-      <c r="M9" t="n">
-        <v>18481.2890625</v>
-      </c>
-      <c r="N9" t="n">
-        <v>18449.859375</v>
-      </c>
-      <c r="O9" t="n">
-        <v>18296.6796875</v>
-      </c>
-      <c r="P9" t="n">
-        <v>18090.8203125</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>73318.6484375</v>
       </c>
     </row>
     <row r="10">
@@ -1005,40 +802,19 @@
         <v>76310.87904395287</v>
       </c>
       <c r="F10" t="n">
-        <v>40443.19735246355</v>
+        <v>13438.25</v>
       </c>
       <c r="G10" t="n">
-        <v>35867.68169148932</v>
+        <v>62.565</v>
       </c>
       <c r="H10" t="n">
-        <v>13438.25</v>
+        <v>916.25</v>
       </c>
       <c r="I10" t="n">
-        <v>62.565</v>
+        <v>205002</v>
       </c>
       <c r="J10" t="n">
-        <v>916.25</v>
-      </c>
-      <c r="K10" t="n">
-        <v>205002</v>
-      </c>
-      <c r="L10" t="n">
         <v>13412.75</v>
-      </c>
-      <c r="M10" t="n">
-        <v>35867.6796875</v>
-      </c>
-      <c r="N10" t="n">
-        <v>35533.1015625</v>
-      </c>
-      <c r="O10" t="n">
-        <v>37040.390625</v>
-      </c>
-      <c r="P10" t="n">
-        <v>36760.87890625</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>145202.05078125</v>
       </c>
     </row>
     <row r="11">
@@ -1062,40 +838,19 @@
         <v>9578.732530662315</v>
       </c>
       <c r="F11" t="n">
-        <v>5132.246844211875</v>
+        <v>1527.75</v>
       </c>
       <c r="G11" t="n">
-        <v>4446.485686450441</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>1527.75</v>
+        <v>160.5</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>17480.5</v>
       </c>
       <c r="J11" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>17480.5</v>
-      </c>
-      <c r="L11" t="n">
         <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4446.490234375</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4629.169921875</v>
-      </c>
-      <c r="O11" t="n">
-        <v>4888.9599609375</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5154.97998046875</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>19119.60009765625</v>
       </c>
     </row>
     <row r="12">
@@ -1119,40 +874,19 @@
         <v>93067.02236377719</v>
       </c>
       <c r="F12" t="n">
-        <v>48265.23501716382</v>
+        <v>16662.25</v>
       </c>
       <c r="G12" t="n">
-        <v>44801.78734661335</v>
+        <v>95.75</v>
       </c>
       <c r="H12" t="n">
-        <v>16662.25</v>
+        <v>714</v>
       </c>
       <c r="I12" t="n">
-        <v>95.75</v>
+        <v>399525.25</v>
       </c>
       <c r="J12" t="n">
-        <v>714</v>
-      </c>
-      <c r="K12" t="n">
-        <v>399525.25</v>
-      </c>
-      <c r="L12" t="n">
         <v>94542.25</v>
-      </c>
-      <c r="M12" t="n">
-        <v>44801.7890625</v>
-      </c>
-      <c r="N12" t="n">
-        <v>45243.94140625</v>
-      </c>
-      <c r="O12" t="n">
-        <v>45558.51171875</v>
-      </c>
-      <c r="P12" t="n">
-        <v>45538.0390625</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>181142.28125</v>
       </c>
     </row>
     <row r="13">
@@ -1176,40 +910,19 @@
         <v>48118.41813851072</v>
       </c>
       <c r="F13" t="n">
-        <v>24340.09649657083</v>
+        <v>13805.75</v>
       </c>
       <c r="G13" t="n">
-        <v>23778.32164193989</v>
+        <v>63.7</v>
       </c>
       <c r="H13" t="n">
-        <v>13805.75</v>
+        <v>185</v>
       </c>
       <c r="I13" t="n">
-        <v>63.7</v>
+        <v>240430</v>
       </c>
       <c r="J13" t="n">
-        <v>185</v>
-      </c>
-      <c r="K13" t="n">
-        <v>240430</v>
-      </c>
-      <c r="L13" t="n">
         <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23778.3203125</v>
-      </c>
-      <c r="N13" t="n">
-        <v>24633.869140625</v>
-      </c>
-      <c r="O13" t="n">
-        <v>25910.490234375</v>
-      </c>
-      <c r="P13" t="n">
-        <v>28188.439453125</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>102511.119140625</v>
       </c>
     </row>
     <row r="14">
@@ -1233,40 +946,19 @@
         <v>16525.05243394294</v>
       </c>
       <c r="F14" t="n">
-        <v>9745.476813861795</v>
+        <v>4614.75</v>
       </c>
       <c r="G14" t="n">
-        <v>6779.575620081139</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>4614.75</v>
+        <v>96.5</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>55689</v>
       </c>
       <c r="J14" t="n">
-        <v>96.5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>55689</v>
-      </c>
-      <c r="L14" t="n">
         <v>58.25</v>
-      </c>
-      <c r="M14" t="n">
-        <v>6774.330078125</v>
-      </c>
-      <c r="N14" t="n">
-        <v>6569.81982421875</v>
-      </c>
-      <c r="O14" t="n">
-        <v>6301.64990234375</v>
-      </c>
-      <c r="P14" t="n">
-        <v>6037.97021484375</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>25683.77001953125</v>
       </c>
     </row>
     <row r="15">
@@ -1290,40 +982,19 @@
         <v>117797.5830022574</v>
       </c>
       <c r="F15" t="n">
-        <v>61730.28783687654</v>
+        <v>29740.25</v>
       </c>
       <c r="G15" t="n">
-        <v>56067.29516538082</v>
+        <v>92</v>
       </c>
       <c r="H15" t="n">
-        <v>29740.25</v>
+        <v>571.5</v>
       </c>
       <c r="I15" t="n">
-        <v>92</v>
+        <v>288416</v>
       </c>
       <c r="J15" t="n">
-        <v>571.5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>288416</v>
-      </c>
-      <c r="L15" t="n">
         <v>127604.5</v>
-      </c>
-      <c r="M15" t="n">
-        <v>56067.30078125</v>
-      </c>
-      <c r="N15" t="n">
-        <v>55818.78125</v>
-      </c>
-      <c r="O15" t="n">
-        <v>55232.921875</v>
-      </c>
-      <c r="P15" t="n">
-        <v>54797.91015625</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>221916.9140625</v>
       </c>
     </row>
     <row r="16">
@@ -1347,40 +1018,19 @@
         <v>170674.4806954099</v>
       </c>
       <c r="F16" t="n">
-        <v>89989.63153419488</v>
+        <v>43962</v>
       </c>
       <c r="G16" t="n">
-        <v>80684.84916121502</v>
+        <v>154</v>
       </c>
       <c r="H16" t="n">
-        <v>43962</v>
+        <v>479</v>
       </c>
       <c r="I16" t="n">
-        <v>154</v>
+        <v>473149.5</v>
       </c>
       <c r="J16" t="n">
-        <v>479</v>
-      </c>
-      <c r="K16" t="n">
-        <v>473149.5</v>
-      </c>
-      <c r="L16" t="n">
         <v>103446.5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>81251.890625</v>
-      </c>
-      <c r="N16" t="n">
-        <v>80101.7578125</v>
-      </c>
-      <c r="O16" t="n">
-        <v>81506.6875</v>
-      </c>
-      <c r="P16" t="n">
-        <v>79912.9765625</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>322773.3125</v>
       </c>
     </row>
     <row r="17">
@@ -1404,40 +1054,19 @@
         <v>15976.36590418797</v>
       </c>
       <c r="F17" t="n">
-        <v>10147.29034588291</v>
+        <v>4162</v>
       </c>
       <c r="G17" t="n">
-        <v>5829.075558305053</v>
+        <v>19.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4162</v>
+        <v>67.5</v>
       </c>
       <c r="I17" t="n">
-        <v>19.5</v>
+        <v>53860.25</v>
       </c>
       <c r="J17" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>53860.25</v>
-      </c>
-      <c r="L17" t="n">
         <v>25632</v>
-      </c>
-      <c r="M17" t="n">
-        <v>5803.509765625</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6226.41015625</v>
-      </c>
-      <c r="O17" t="n">
-        <v>6647.580078125</v>
-      </c>
-      <c r="P17" t="n">
-        <v>6442.830078125</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>25120.330078125</v>
       </c>
     </row>
     <row r="18">
@@ -1461,40 +1090,19 @@
         <v>103336.1499209229</v>
       </c>
       <c r="F18" t="n">
-        <v>56421.93143073621</v>
+        <v>28384.75</v>
       </c>
       <c r="G18" t="n">
-        <v>46914.21849018671</v>
+        <v>149</v>
       </c>
       <c r="H18" t="n">
-        <v>28384.75</v>
+        <v>360.5</v>
       </c>
       <c r="I18" t="n">
-        <v>149</v>
+        <v>329180.75</v>
       </c>
       <c r="J18" t="n">
-        <v>360.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>329180.75</v>
-      </c>
-      <c r="L18" t="n">
         <v>156867</v>
-      </c>
-      <c r="M18" t="n">
-        <v>47171.30078125</v>
-      </c>
-      <c r="N18" t="n">
-        <v>49253.9296875</v>
-      </c>
-      <c r="O18" t="n">
-        <v>50464.83984375</v>
-      </c>
-      <c r="P18" t="n">
-        <v>51815.19921875</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>198705.26953125</v>
       </c>
     </row>
     <row r="19">
@@ -1518,40 +1126,19 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>15726.5</v>
+      </c>
+      <c r="J19" t="n">
         <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>20</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>15726.5</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>23.03000068664551</v>
-      </c>
-      <c r="N19" t="n">
-        <v>21.82999992370605</v>
-      </c>
-      <c r="O19" t="n">
-        <v>20.63999938964844</v>
-      </c>
-      <c r="P19" t="n">
-        <v>19.55999946594238</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>85.05999946594238</v>
       </c>
     </row>
     <row r="20">
@@ -1575,40 +1162,19 @@
         <v>15333.17547869867</v>
       </c>
       <c r="F20" t="n">
-        <v>9340.63215083355</v>
+        <v>4539.25</v>
       </c>
       <c r="G20" t="n">
-        <v>5992.543327865115</v>
+        <v>16.9675</v>
       </c>
       <c r="H20" t="n">
-        <v>4539.25</v>
+        <v>123.25</v>
       </c>
       <c r="I20" t="n">
-        <v>16.9675</v>
+        <v>58148.25</v>
       </c>
       <c r="J20" t="n">
-        <v>123.25</v>
-      </c>
-      <c r="K20" t="n">
-        <v>58148.25</v>
-      </c>
-      <c r="L20" t="n">
         <v>7860</v>
-      </c>
-      <c r="M20" t="n">
-        <v>5992.5400390625</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5833.18994140625</v>
-      </c>
-      <c r="O20" t="n">
-        <v>5667.5400390625</v>
-      </c>
-      <c r="P20" t="n">
-        <v>5552.240234375</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>23045.51025390625</v>
       </c>
     </row>
     <row r="21">
@@ -1632,40 +1198,19 @@
         <v>14579.05876170755</v>
       </c>
       <c r="F21" t="n">
-        <v>8623.259595633137</v>
+        <v>3521.25</v>
       </c>
       <c r="G21" t="n">
-        <v>5955.799166074411</v>
+        <v>15</v>
       </c>
       <c r="H21" t="n">
-        <v>3521.25</v>
+        <v>247.25</v>
       </c>
       <c r="I21" t="n">
-        <v>15</v>
+        <v>54692.5</v>
       </c>
       <c r="J21" t="n">
-        <v>247.25</v>
-      </c>
-      <c r="K21" t="n">
-        <v>54692.5</v>
-      </c>
-      <c r="L21" t="n">
         <v>3807.25</v>
-      </c>
-      <c r="M21" t="n">
-        <v>5955.7998046875</v>
-      </c>
-      <c r="N21" t="n">
-        <v>6053.60986328125</v>
-      </c>
-      <c r="O21" t="n">
-        <v>5981.240234375</v>
-      </c>
-      <c r="P21" t="n">
-        <v>5894.39990234375</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>23885.0498046875</v>
       </c>
     </row>
     <row r="22">
@@ -1689,40 +1234,19 @@
         <v>19364.95898535976</v>
       </c>
       <c r="F22" t="n">
-        <v>11881.68356106935</v>
+        <v>6440.75</v>
       </c>
       <c r="G22" t="n">
-        <v>7483.275424290419</v>
+        <v>23.075</v>
       </c>
       <c r="H22" t="n">
-        <v>6440.75</v>
+        <v>91.5</v>
       </c>
       <c r="I22" t="n">
-        <v>23.075</v>
+        <v>64243.25</v>
       </c>
       <c r="J22" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>64243.25</v>
-      </c>
-      <c r="L22" t="n">
         <v>31189.25</v>
-      </c>
-      <c r="M22" t="n">
-        <v>7483.27978515625</v>
-      </c>
-      <c r="N22" t="n">
-        <v>7384.43994140625</v>
-      </c>
-      <c r="O22" t="n">
-        <v>7221.27978515625</v>
-      </c>
-      <c r="P22" t="n">
-        <v>7718.580078125</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>29807.57958984375</v>
       </c>
     </row>
     <row r="23">
@@ -1746,40 +1270,19 @@
         <v>19033.43668260284</v>
       </c>
       <c r="F23" t="n">
-        <v>10403.34629132059</v>
+        <v>3158</v>
       </c>
       <c r="G23" t="n">
-        <v>8630.090391282249</v>
+        <v>28</v>
       </c>
       <c r="H23" t="n">
-        <v>3158</v>
+        <v>140.5</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>41544</v>
       </c>
       <c r="J23" t="n">
-        <v>140.5</v>
-      </c>
-      <c r="K23" t="n">
-        <v>41544</v>
-      </c>
-      <c r="L23" t="n">
         <v>67986.75</v>
-      </c>
-      <c r="M23" t="n">
-        <v>8630.08984375</v>
-      </c>
-      <c r="N23" t="n">
-        <v>8866</v>
-      </c>
-      <c r="O23" t="n">
-        <v>8741.4404296875</v>
-      </c>
-      <c r="P23" t="n">
-        <v>8932.3798828125</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>35169.91015625</v>
       </c>
     </row>
     <row r="24">
@@ -1803,40 +1306,19 @@
         <v>134357.0478898294</v>
       </c>
       <c r="F24" t="n">
-        <v>75523.22679432326</v>
+        <v>41969</v>
       </c>
       <c r="G24" t="n">
-        <v>58833.82109550619</v>
+        <v>281.75</v>
       </c>
       <c r="H24" t="n">
-        <v>41969</v>
+        <v>415</v>
       </c>
       <c r="I24" t="n">
-        <v>281.75</v>
+        <v>491031.75</v>
       </c>
       <c r="J24" t="n">
-        <v>415</v>
-      </c>
-      <c r="K24" t="n">
-        <v>491031.75</v>
-      </c>
-      <c r="L24" t="n">
         <v>310043.25</v>
-      </c>
-      <c r="M24" t="n">
-        <v>58833.8203125</v>
-      </c>
-      <c r="N24" t="n">
-        <v>59100.80078125</v>
-      </c>
-      <c r="O24" t="n">
-        <v>59099.69921875</v>
-      </c>
-      <c r="P24" t="n">
-        <v>57752.33984375</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>234786.66015625</v>
       </c>
     </row>
     <row r="25">
@@ -1860,40 +1342,19 @@
         <v>152438.027880248</v>
       </c>
       <c r="F25" t="n">
-        <v>82131.36063944336</v>
+        <v>47836.5</v>
       </c>
       <c r="G25" t="n">
-        <v>70306.66724080463</v>
+        <v>133</v>
       </c>
       <c r="H25" t="n">
-        <v>47836.5</v>
+        <v>579.5</v>
       </c>
       <c r="I25" t="n">
-        <v>133</v>
+        <v>451668.5</v>
       </c>
       <c r="J25" t="n">
-        <v>579.5</v>
-      </c>
-      <c r="K25" t="n">
-        <v>451668.5</v>
-      </c>
-      <c r="L25" t="n">
         <v>182113</v>
-      </c>
-      <c r="M25" t="n">
-        <v>70306.65625</v>
-      </c>
-      <c r="N25" t="n">
-        <v>75046.2578125</v>
-      </c>
-      <c r="O25" t="n">
-        <v>78366.703125</v>
-      </c>
-      <c r="P25" t="n">
-        <v>83830.4609375</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>307550.078125</v>
       </c>
     </row>
     <row r="26">
@@ -1917,40 +1378,19 @@
         <v>102997.3411977229</v>
       </c>
       <c r="F26" t="n">
-        <v>53243.39019161568</v>
+        <v>17199.5</v>
       </c>
       <c r="G26" t="n">
-        <v>49753.95100610724</v>
+        <v>76</v>
       </c>
       <c r="H26" t="n">
-        <v>17199.5</v>
+        <v>872.5</v>
       </c>
       <c r="I26" t="n">
-        <v>76</v>
+        <v>224815.75</v>
       </c>
       <c r="J26" t="n">
-        <v>872.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>224815.75</v>
-      </c>
-      <c r="L26" t="n">
         <v>92039</v>
-      </c>
-      <c r="M26" t="n">
-        <v>51076.1484375</v>
-      </c>
-      <c r="N26" t="n">
-        <v>50764.0390625</v>
-      </c>
-      <c r="O26" t="n">
-        <v>50545.578125</v>
-      </c>
-      <c r="P26" t="n">
-        <v>50295.921875</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>202681.6875</v>
       </c>
     </row>
     <row r="27">
@@ -1974,40 +1414,19 @@
         <v>61077.34663178231</v>
       </c>
       <c r="F27" t="n">
-        <v>33211.04434657552</v>
+        <v>15202.5</v>
       </c>
       <c r="G27" t="n">
-        <v>27866.30228520678</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>15202.5</v>
+        <v>198.25</v>
       </c>
       <c r="I27" t="n">
-        <v>82.90000000000001</v>
+        <v>202127.25</v>
       </c>
       <c r="J27" t="n">
-        <v>198.25</v>
-      </c>
-      <c r="K27" t="n">
-        <v>202127.25</v>
-      </c>
-      <c r="L27" t="n">
         <v>149139.75</v>
-      </c>
-      <c r="M27" t="n">
-        <v>27866.30078125</v>
-      </c>
-      <c r="N27" t="n">
-        <v>30489.439453125</v>
-      </c>
-      <c r="O27" t="n">
-        <v>30519.5703125</v>
-      </c>
-      <c r="P27" t="n">
-        <v>30095.0703125</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>118970.380859375</v>
       </c>
     </row>
     <row r="28">
@@ -2031,40 +1450,19 @@
         <v>13680.32995890737</v>
       </c>
       <c r="F28" t="n">
-        <v>7665.721152722506</v>
+        <v>3204.75</v>
       </c>
       <c r="G28" t="n">
-        <v>6014.608806184861</v>
+        <v>14.8225</v>
       </c>
       <c r="H28" t="n">
-        <v>3204.75</v>
+        <v>50.5</v>
       </c>
       <c r="I28" t="n">
-        <v>14.8225</v>
+        <v>46220.25</v>
       </c>
       <c r="J28" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="K28" t="n">
-        <v>46220.25</v>
-      </c>
-      <c r="L28" t="n">
         <v>14142.75</v>
-      </c>
-      <c r="M28" t="n">
-        <v>6014.60986328125</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5839.83984375</v>
-      </c>
-      <c r="O28" t="n">
-        <v>5696.52001953125</v>
-      </c>
-      <c r="P28" t="n">
-        <v>5486.169921875</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>23037.1396484375</v>
       </c>
     </row>
     <row r="29">
@@ -2088,40 +1486,19 @@
         <v>21711.71831709049</v>
       </c>
       <c r="F29" t="n">
-        <v>13501.64519405736</v>
+        <v>4835.75</v>
       </c>
       <c r="G29" t="n">
-        <v>8210.073123033131</v>
+        <v>35.25</v>
       </c>
       <c r="H29" t="n">
-        <v>4835.75</v>
+        <v>141.75</v>
       </c>
       <c r="I29" t="n">
-        <v>35.25</v>
+        <v>84174</v>
       </c>
       <c r="J29" t="n">
-        <v>141.75</v>
-      </c>
-      <c r="K29" t="n">
-        <v>84174</v>
-      </c>
-      <c r="L29" t="n">
         <v>68267.25</v>
-      </c>
-      <c r="M29" t="n">
-        <v>8210.0703125</v>
-      </c>
-      <c r="N29" t="n">
-        <v>8273.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>8560.5</v>
-      </c>
-      <c r="P29" t="n">
-        <v>11411.8603515625</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>36455.9306640625</v>
       </c>
     </row>
     <row r="30">
@@ -2145,40 +1522,19 @@
         <v>28763.94178261566</v>
       </c>
       <c r="F30" t="n">
-        <v>14995.20636834866</v>
+        <v>4179</v>
       </c>
       <c r="G30" t="n">
-        <v>13768.735414267</v>
+        <v>16.7775</v>
       </c>
       <c r="H30" t="n">
-        <v>4179</v>
+        <v>341.25</v>
       </c>
       <c r="I30" t="n">
-        <v>16.7775</v>
+        <v>56646.5</v>
       </c>
       <c r="J30" t="n">
-        <v>341.25</v>
-      </c>
-      <c r="K30" t="n">
-        <v>56646.5</v>
-      </c>
-      <c r="L30" t="n">
         <v>11075.75</v>
-      </c>
-      <c r="M30" t="n">
-        <v>13768.740234375</v>
-      </c>
-      <c r="N30" t="n">
-        <v>13801.0703125</v>
-      </c>
-      <c r="O30" t="n">
-        <v>13575.1904296875</v>
-      </c>
-      <c r="P30" t="n">
-        <v>13312.3603515625</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>54457.361328125</v>
       </c>
     </row>
     <row r="31">
@@ -2202,40 +1558,19 @@
         <v>727481.5155850692</v>
       </c>
       <c r="F31" t="n">
-        <v>390904.2393409224</v>
+        <v>268270.25</v>
       </c>
       <c r="G31" t="n">
-        <v>336577.2762441467</v>
+        <v>874.75</v>
       </c>
       <c r="H31" t="n">
-        <v>268270.25</v>
+        <v>1582.5</v>
       </c>
       <c r="I31" t="n">
-        <v>874.75</v>
+        <v>2728069.5</v>
       </c>
       <c r="J31" t="n">
-        <v>1582.5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2728069.5</v>
-      </c>
-      <c r="L31" t="n">
         <v>1615341.75</v>
-      </c>
-      <c r="M31" t="n">
-        <v>336577.28125</v>
-      </c>
-      <c r="N31" t="n">
-        <v>353823.15625</v>
-      </c>
-      <c r="O31" t="n">
-        <v>361233.1875</v>
-      </c>
-      <c r="P31" t="n">
-        <v>363401.84375</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1415035.46875</v>
       </c>
     </row>
     <row r="32">
@@ -2259,40 +1594,19 @@
         <v>29938.33241573288</v>
       </c>
       <c r="F32" t="n">
-        <v>15232.15468445241</v>
+        <v>4946.25</v>
       </c>
       <c r="G32" t="n">
-        <v>14706.17773128046</v>
+        <v>25.505</v>
       </c>
       <c r="H32" t="n">
-        <v>4946.25</v>
+        <v>214</v>
       </c>
       <c r="I32" t="n">
-        <v>25.505</v>
+        <v>78186.5</v>
       </c>
       <c r="J32" t="n">
-        <v>214</v>
-      </c>
-      <c r="K32" t="n">
-        <v>78186.5</v>
-      </c>
-      <c r="L32" t="n">
         <v>17294.75</v>
-      </c>
-      <c r="M32" t="n">
-        <v>14706.1796875</v>
-      </c>
-      <c r="N32" t="n">
-        <v>16305.7197265625</v>
-      </c>
-      <c r="O32" t="n">
-        <v>16083.5400390625</v>
-      </c>
-      <c r="P32" t="n">
-        <v>15748.5595703125</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>62843.9990234375</v>
       </c>
     </row>
     <row r="33">
@@ -2316,40 +1630,19 @@
         <v>4016.738971000253</v>
       </c>
       <c r="F33" t="n">
-        <v>2766.200252185317</v>
+        <v>1811.5</v>
       </c>
       <c r="G33" t="n">
-        <v>1250.538718814934</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>1811.5</v>
+        <v>27</v>
       </c>
       <c r="I33" t="n">
-        <v>7</v>
+        <v>24982.5</v>
       </c>
       <c r="J33" t="n">
-        <v>27</v>
-      </c>
-      <c r="K33" t="n">
-        <v>24982.5</v>
-      </c>
-      <c r="L33" t="n">
         <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1250.5400390625</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1164.069946289062</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1103.670043945312</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1041.359985351562</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4559.640014648436</v>
       </c>
     </row>
     <row r="34">
@@ -2373,40 +1666,19 @@
         <v>23411.02567746788</v>
       </c>
       <c r="F34" t="n">
-        <v>12239.12746608726</v>
+        <v>5286.25</v>
       </c>
       <c r="G34" t="n">
-        <v>11171.89821138062</v>
+        <v>23.775</v>
       </c>
       <c r="H34" t="n">
-        <v>5286.25</v>
+        <v>335.5</v>
       </c>
       <c r="I34" t="n">
-        <v>23.775</v>
+        <v>74483.75</v>
       </c>
       <c r="J34" t="n">
-        <v>335.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>74483.75</v>
-      </c>
-      <c r="L34" t="n">
         <v>22173.5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>11171.900390625</v>
-      </c>
-      <c r="N34" t="n">
-        <v>10900.6796875</v>
-      </c>
-      <c r="O34" t="n">
-        <v>10563.5595703125</v>
-      </c>
-      <c r="P34" t="n">
-        <v>10206.900390625</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>42843.0400390625</v>
       </c>
     </row>
     <row r="35">
@@ -2430,40 +1702,19 @@
         <v>9803.195266708623</v>
       </c>
       <c r="F35" t="n">
-        <v>4791.214254994316</v>
+        <v>2019.25</v>
       </c>
       <c r="G35" t="n">
-        <v>5011.981011714307</v>
+        <v>7.25</v>
       </c>
       <c r="H35" t="n">
-        <v>2019.25</v>
+        <v>126.25</v>
       </c>
       <c r="I35" t="n">
-        <v>7.25</v>
+        <v>26127.75</v>
       </c>
       <c r="J35" t="n">
-        <v>126.25</v>
-      </c>
-      <c r="K35" t="n">
-        <v>26127.75</v>
-      </c>
-      <c r="L35" t="n">
         <v>36.25</v>
-      </c>
-      <c r="M35" t="n">
-        <v>5011.97998046875</v>
-      </c>
-      <c r="N35" t="n">
-        <v>4849.7001953125</v>
-      </c>
-      <c r="O35" t="n">
-        <v>4694.10009765625</v>
-      </c>
-      <c r="P35" t="n">
-        <v>4562.18994140625</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>19117.97021484375</v>
       </c>
     </row>
     <row r="36">
@@ -2487,40 +1738,19 @@
         <v>21893.39989712041</v>
       </c>
       <c r="F36" t="n">
-        <v>14096.57834071484</v>
+        <v>6499.75</v>
       </c>
       <c r="G36" t="n">
-        <v>7796.821556405565</v>
+        <v>22.1675</v>
       </c>
       <c r="H36" t="n">
-        <v>6499.75</v>
+        <v>260.75</v>
       </c>
       <c r="I36" t="n">
-        <v>22.1675</v>
+        <v>76661.5</v>
       </c>
       <c r="J36" t="n">
-        <v>260.75</v>
-      </c>
-      <c r="K36" t="n">
-        <v>76661.5</v>
-      </c>
-      <c r="L36" t="n">
         <v>6517.5</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7796.81982421875</v>
-      </c>
-      <c r="N36" t="n">
-        <v>8529.4404296875</v>
-      </c>
-      <c r="O36" t="n">
-        <v>9058.51953125</v>
-      </c>
-      <c r="P36" t="n">
-        <v>8770.5</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>34155.27978515625</v>
       </c>
     </row>
     <row r="37">
@@ -2544,40 +1774,19 @@
         <v>69474.49914039478</v>
       </c>
       <c r="F37" t="n">
-        <v>39383.26808732434</v>
+        <v>13850</v>
       </c>
       <c r="G37" t="n">
-        <v>30091.23105307043</v>
+        <v>70.33</v>
       </c>
       <c r="H37" t="n">
-        <v>13850</v>
+        <v>579</v>
       </c>
       <c r="I37" t="n">
-        <v>70.33</v>
+        <v>193731</v>
       </c>
       <c r="J37" t="n">
-        <v>579</v>
-      </c>
-      <c r="K37" t="n">
-        <v>193731</v>
-      </c>
-      <c r="L37" t="n">
         <v>70340.5</v>
-      </c>
-      <c r="M37" t="n">
-        <v>30091.23046875</v>
-      </c>
-      <c r="N37" t="n">
-        <v>29349.380859375</v>
-      </c>
-      <c r="O37" t="n">
-        <v>28716.640625</v>
-      </c>
-      <c r="P37" t="n">
-        <v>27974.919921875</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>116132.171875</v>
       </c>
     </row>
     <row r="38">
@@ -2601,40 +1810,19 @@
         <v>90357.95076973521</v>
       </c>
       <c r="F38" t="n">
-        <v>44709.58013856956</v>
+        <v>14389.5</v>
       </c>
       <c r="G38" t="n">
-        <v>45648.37063116565</v>
+        <v>77.8</v>
       </c>
       <c r="H38" t="n">
-        <v>14389.5</v>
+        <v>410</v>
       </c>
       <c r="I38" t="n">
-        <v>77.8</v>
+        <v>237473.75</v>
       </c>
       <c r="J38" t="n">
-        <v>410</v>
-      </c>
-      <c r="K38" t="n">
-        <v>237473.75</v>
-      </c>
-      <c r="L38" t="n">
         <v>63380.5</v>
-      </c>
-      <c r="M38" t="n">
-        <v>45652.0390625</v>
-      </c>
-      <c r="N38" t="n">
-        <v>45210</v>
-      </c>
-      <c r="O38" t="n">
-        <v>44748.1796875</v>
-      </c>
-      <c r="P38" t="n">
-        <v>44291.55859375</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>179901.77734375</v>
       </c>
     </row>
     <row r="39">
@@ -2658,40 +1846,19 @@
         <v>68578.1433617432</v>
       </c>
       <c r="F39" t="n">
-        <v>38529.39979152534</v>
+        <v>15460</v>
       </c>
       <c r="G39" t="n">
-        <v>30048.74357021786</v>
+        <v>79.03999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>15460</v>
+        <v>357</v>
       </c>
       <c r="I39" t="n">
-        <v>79.03999999999999</v>
+        <v>229524.75</v>
       </c>
       <c r="J39" t="n">
-        <v>357</v>
-      </c>
-      <c r="K39" t="n">
-        <v>229524.75</v>
-      </c>
-      <c r="L39" t="n">
         <v>47525.25</v>
-      </c>
-      <c r="M39" t="n">
-        <v>30068.669921875</v>
-      </c>
-      <c r="N39" t="n">
-        <v>29616.890625</v>
-      </c>
-      <c r="O39" t="n">
-        <v>29918.4296875</v>
-      </c>
-      <c r="P39" t="n">
-        <v>29744.580078125</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>119348.5703125</v>
       </c>
     </row>
     <row r="40">
@@ -2715,40 +1882,19 @@
         <v>15437.2428455211</v>
       </c>
       <c r="F40" t="n">
-        <v>7564.378696777042</v>
+        <v>2504.25</v>
       </c>
       <c r="G40" t="n">
-        <v>7872.864148744061</v>
+        <v>17.775</v>
       </c>
       <c r="H40" t="n">
-        <v>2504.25</v>
+        <v>152.25</v>
       </c>
       <c r="I40" t="n">
-        <v>17.775</v>
+        <v>48806.75</v>
       </c>
       <c r="J40" t="n">
-        <v>152.25</v>
-      </c>
-      <c r="K40" t="n">
-        <v>48806.75</v>
-      </c>
-      <c r="L40" t="n">
         <v>11225.5</v>
-      </c>
-      <c r="M40" t="n">
-        <v>7606.39013671875</v>
-      </c>
-      <c r="N40" t="n">
-        <v>7740.080078125</v>
-      </c>
-      <c r="O40" t="n">
-        <v>7901.93017578125</v>
-      </c>
-      <c r="P40" t="n">
-        <v>8048.47021484375</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>31296.87060546875</v>
       </c>
     </row>
     <row r="41">
@@ -2772,40 +1918,19 @@
         <v>389003.365004319</v>
       </c>
       <c r="F41" t="n">
-        <v>202168.9156980356</v>
+        <v>62737.75</v>
       </c>
       <c r="G41" t="n">
-        <v>186834.4493062834</v>
+        <v>369.85</v>
       </c>
       <c r="H41" t="n">
-        <v>62737.75</v>
+        <v>2854.5</v>
       </c>
       <c r="I41" t="n">
-        <v>369.85</v>
+        <v>867106.5</v>
       </c>
       <c r="J41" t="n">
-        <v>2854.5</v>
-      </c>
-      <c r="K41" t="n">
-        <v>867106.5</v>
-      </c>
-      <c r="L41" t="n">
         <v>228524</v>
-      </c>
-      <c r="M41" t="n">
-        <v>186581.015625</v>
-      </c>
-      <c r="N41" t="n">
-        <v>190702.28125</v>
-      </c>
-      <c r="O41" t="n">
-        <v>189363.515625</v>
-      </c>
-      <c r="P41" t="n">
-        <v>185445.9375</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>752092.75</v>
       </c>
     </row>
     <row r="42">
@@ -2829,40 +1954,19 @@
         <v>233008.493411261</v>
       </c>
       <c r="F42" t="n">
-        <v>123172.8603647108</v>
+        <v>56695.5</v>
       </c>
       <c r="G42" t="n">
-        <v>109835.6330465502</v>
+        <v>217.75</v>
       </c>
       <c r="H42" t="n">
-        <v>56695.5</v>
+        <v>984.75</v>
       </c>
       <c r="I42" t="n">
-        <v>217.75</v>
+        <v>739901.25</v>
       </c>
       <c r="J42" t="n">
-        <v>984.75</v>
-      </c>
-      <c r="K42" t="n">
-        <v>739901.25</v>
-      </c>
-      <c r="L42" t="n">
         <v>307464.25</v>
-      </c>
-      <c r="M42" t="n">
-        <v>111387.6875</v>
-      </c>
-      <c r="N42" t="n">
-        <v>120853.796875</v>
-      </c>
-      <c r="O42" t="n">
-        <v>124487.3515625</v>
-      </c>
-      <c r="P42" t="n">
-        <v>127136.21875</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>483865.0546875</v>
       </c>
     </row>
     <row r="43">
@@ -2886,40 +1990,19 @@
         <v>66589.37313193572</v>
       </c>
       <c r="F43" t="n">
-        <v>37052.54084427303</v>
+        <v>24123.75</v>
       </c>
       <c r="G43" t="n">
-        <v>29536.8322876627</v>
+        <v>78</v>
       </c>
       <c r="H43" t="n">
-        <v>24123.75</v>
+        <v>217.75</v>
       </c>
       <c r="I43" t="n">
-        <v>78</v>
+        <v>262576.25</v>
       </c>
       <c r="J43" t="n">
-        <v>217.75</v>
-      </c>
-      <c r="K43" t="n">
-        <v>262576.25</v>
-      </c>
-      <c r="L43" t="n">
         <v>111283</v>
-      </c>
-      <c r="M43" t="n">
-        <v>29536.830078125</v>
-      </c>
-      <c r="N43" t="n">
-        <v>29298.2109375</v>
-      </c>
-      <c r="O43" t="n">
-        <v>29097.869140625</v>
-      </c>
-      <c r="P43" t="n">
-        <v>28900.51953125</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>116833.4296875</v>
       </c>
     </row>
     <row r="44">
@@ -2943,40 +2026,19 @@
         <v>79083.6039143331</v>
       </c>
       <c r="F44" t="n">
-        <v>49217.13352076753</v>
+        <v>15500.25</v>
       </c>
       <c r="G44" t="n">
-        <v>29866.47039356558</v>
+        <v>93</v>
       </c>
       <c r="H44" t="n">
-        <v>15500.25</v>
+        <v>522.5</v>
       </c>
       <c r="I44" t="n">
-        <v>93</v>
+        <v>227344</v>
       </c>
       <c r="J44" t="n">
-        <v>522.5</v>
-      </c>
-      <c r="K44" t="n">
-        <v>227344</v>
-      </c>
-      <c r="L44" t="n">
         <v>164974.75</v>
-      </c>
-      <c r="M44" t="n">
-        <v>29866.470703125</v>
-      </c>
-      <c r="N44" t="n">
-        <v>29876.48046875</v>
-      </c>
-      <c r="O44" t="n">
-        <v>29899.740234375</v>
-      </c>
-      <c r="P44" t="n">
-        <v>30039.1796875</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>119681.87109375</v>
       </c>
     </row>
     <row r="45">
@@ -3000,40 +2062,19 @@
         <v>77428.93834624006</v>
       </c>
       <c r="F45" t="n">
-        <v>44131.75778490175</v>
+        <v>19749.5</v>
       </c>
       <c r="G45" t="n">
-        <v>33297.18056133832</v>
+        <v>89</v>
       </c>
       <c r="H45" t="n">
-        <v>19749.5</v>
+        <v>217</v>
       </c>
       <c r="I45" t="n">
-        <v>89</v>
+        <v>233857.5</v>
       </c>
       <c r="J45" t="n">
-        <v>217</v>
-      </c>
-      <c r="K45" t="n">
-        <v>233857.5</v>
-      </c>
-      <c r="L45" t="n">
         <v>116894</v>
-      </c>
-      <c r="M45" t="n">
-        <v>33389.078125</v>
-      </c>
-      <c r="N45" t="n">
-        <v>33913.16015625</v>
-      </c>
-      <c r="O45" t="n">
-        <v>34238.58984375</v>
-      </c>
-      <c r="P45" t="n">
-        <v>34597.390625</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>136138.21875</v>
       </c>
     </row>
     <row r="46">
@@ -3057,40 +2098,19 @@
         <v>119270.2440331175</v>
       </c>
       <c r="F46" t="n">
-        <v>64030.35734684167</v>
+        <v>34300.25</v>
       </c>
       <c r="G46" t="n">
-        <v>55239.88668627585</v>
+        <v>113.25</v>
       </c>
       <c r="H46" t="n">
-        <v>34300.25</v>
+        <v>375.75</v>
       </c>
       <c r="I46" t="n">
-        <v>113.25</v>
+        <v>366646.75</v>
       </c>
       <c r="J46" t="n">
-        <v>375.75</v>
-      </c>
-      <c r="K46" t="n">
-        <v>366646.75</v>
-      </c>
-      <c r="L46" t="n">
         <v>158677.5</v>
-      </c>
-      <c r="M46" t="n">
-        <v>55239.87890625</v>
-      </c>
-      <c r="N46" t="n">
-        <v>55555.3984375</v>
-      </c>
-      <c r="O46" t="n">
-        <v>58561.37890625</v>
-      </c>
-      <c r="P46" t="n">
-        <v>62202.98828125</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>231559.64453125</v>
       </c>
     </row>
     <row r="47">
@@ -3114,40 +2134,19 @@
         <v>73673.18493112596</v>
       </c>
       <c r="F47" t="n">
-        <v>39226.00088864001</v>
+        <v>18000</v>
       </c>
       <c r="G47" t="n">
-        <v>34447.18404248595</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>18000</v>
+        <v>904</v>
       </c>
       <c r="I47" t="n">
-        <v>82.59999999999999</v>
+        <v>228391</v>
       </c>
       <c r="J47" t="n">
-        <v>904</v>
-      </c>
-      <c r="K47" t="n">
-        <v>228391</v>
-      </c>
-      <c r="L47" t="n">
         <v>133973.5</v>
-      </c>
-      <c r="M47" t="n">
-        <v>34447.1796875</v>
-      </c>
-      <c r="N47" t="n">
-        <v>35023.53125</v>
-      </c>
-      <c r="O47" t="n">
-        <v>36040.01953125</v>
-      </c>
-      <c r="P47" t="n">
-        <v>37124.359375</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>142635.08984375</v>
       </c>
     </row>
     <row r="48">
@@ -3171,40 +2170,19 @@
         <v>55886.67131760898</v>
       </c>
       <c r="F48" t="n">
-        <v>28955.23324889571</v>
+        <v>10413.5</v>
       </c>
       <c r="G48" t="n">
-        <v>26931.43806871327</v>
+        <v>42.2825</v>
       </c>
       <c r="H48" t="n">
-        <v>10413.5</v>
+        <v>302.75</v>
       </c>
       <c r="I48" t="n">
-        <v>42.2825</v>
+        <v>145437.5</v>
       </c>
       <c r="J48" t="n">
-        <v>302.75</v>
-      </c>
-      <c r="K48" t="n">
-        <v>145437.5</v>
-      </c>
-      <c r="L48" t="n">
         <v>42680.5</v>
-      </c>
-      <c r="M48" t="n">
-        <v>26931.439453125</v>
-      </c>
-      <c r="N48" t="n">
-        <v>26745.330078125</v>
-      </c>
-      <c r="O48" t="n">
-        <v>26454.1796875</v>
-      </c>
-      <c r="P48" t="n">
-        <v>26337.849609375</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>106468.798828125</v>
       </c>
     </row>
     <row r="49">
@@ -3228,40 +2206,19 @@
         <v>102179.7121577923</v>
       </c>
       <c r="F49" t="n">
-        <v>51259.68223104157</v>
+        <v>23003.75</v>
       </c>
       <c r="G49" t="n">
-        <v>50920.02992675069</v>
+        <v>97.5</v>
       </c>
       <c r="H49" t="n">
-        <v>23003.75</v>
+        <v>857.25</v>
       </c>
       <c r="I49" t="n">
-        <v>97.5</v>
+        <v>313306.5</v>
       </c>
       <c r="J49" t="n">
-        <v>857.25</v>
-      </c>
-      <c r="K49" t="n">
-        <v>313306.5</v>
-      </c>
-      <c r="L49" t="n">
         <v>64628.5</v>
-      </c>
-      <c r="M49" t="n">
-        <v>50920.03125</v>
-      </c>
-      <c r="N49" t="n">
-        <v>53773.0390625</v>
-      </c>
-      <c r="O49" t="n">
-        <v>55291.078125</v>
-      </c>
-      <c r="P49" t="n">
-        <v>57445.55859375</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>217429.70703125</v>
       </c>
     </row>
     <row r="50">
@@ -3285,40 +2242,19 @@
         <v>55498.13213271486</v>
       </c>
       <c r="F50" t="n">
-        <v>32135.35554399303</v>
+        <v>19061.5</v>
       </c>
       <c r="G50" t="n">
-        <v>23362.77658872184</v>
+        <v>80.5</v>
       </c>
       <c r="H50" t="n">
-        <v>19061.5</v>
+        <v>130.5</v>
       </c>
       <c r="I50" t="n">
-        <v>80.5</v>
+        <v>157567</v>
       </c>
       <c r="J50" t="n">
-        <v>130.5</v>
-      </c>
-      <c r="K50" t="n">
-        <v>157567</v>
-      </c>
-      <c r="L50" t="n">
         <v>214690.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>23362.779296875</v>
-      </c>
-      <c r="N50" t="n">
-        <v>24796.919921875</v>
-      </c>
-      <c r="O50" t="n">
-        <v>26590.560546875</v>
-      </c>
-      <c r="P50" t="n">
-        <v>27817.060546875</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>102567.3203125</v>
       </c>
     </row>
     <row r="51">
@@ -3342,40 +2278,19 @@
         <v>78798.84661994684</v>
       </c>
       <c r="F51" t="n">
-        <v>38235.23846697779</v>
+        <v>17925</v>
       </c>
       <c r="G51" t="n">
-        <v>40563.60815296904</v>
+        <v>75.55</v>
       </c>
       <c r="H51" t="n">
-        <v>17925</v>
+        <v>385.75</v>
       </c>
       <c r="I51" t="n">
-        <v>75.55</v>
+        <v>277455.75</v>
       </c>
       <c r="J51" t="n">
-        <v>385.75</v>
-      </c>
-      <c r="K51" t="n">
-        <v>277455.75</v>
-      </c>
-      <c r="L51" t="n">
         <v>9398.5</v>
-      </c>
-      <c r="M51" t="n">
-        <v>40563.609375</v>
-      </c>
-      <c r="N51" t="n">
-        <v>41636.46875</v>
-      </c>
-      <c r="O51" t="n">
-        <v>41644.4296875</v>
-      </c>
-      <c r="P51" t="n">
-        <v>41635.890625</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>165480.3984375</v>
       </c>
     </row>
     <row r="52">
@@ -3399,40 +2314,19 @@
         <v>206620.1748288542</v>
       </c>
       <c r="F52" t="n">
-        <v>113309.4778812093</v>
+        <v>76287</v>
       </c>
       <c r="G52" t="n">
-        <v>93310.69694764486</v>
+        <v>225.525</v>
       </c>
       <c r="H52" t="n">
-        <v>76287</v>
+        <v>1406</v>
       </c>
       <c r="I52" t="n">
-        <v>225.525</v>
+        <v>747833.25</v>
       </c>
       <c r="J52" t="n">
-        <v>1406</v>
-      </c>
-      <c r="K52" t="n">
-        <v>747833.25</v>
-      </c>
-      <c r="L52" t="n">
         <v>412477</v>
-      </c>
-      <c r="M52" t="n">
-        <v>100514.03125</v>
-      </c>
-      <c r="N52" t="n">
-        <v>104680.1875</v>
-      </c>
-      <c r="O52" t="n">
-        <v>109851.5</v>
-      </c>
-      <c r="P52" t="n">
-        <v>114625.640625</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>429671.359375</v>
       </c>
     </row>
     <row r="53">
@@ -3456,40 +2350,19 @@
         <v>29521.96464211315</v>
       </c>
       <c r="F53" t="n">
-        <v>17685.1667013181</v>
+        <v>9178.75</v>
       </c>
       <c r="G53" t="n">
-        <v>11836.79794079506</v>
+        <v>40.5</v>
       </c>
       <c r="H53" t="n">
-        <v>9178.75</v>
+        <v>111</v>
       </c>
       <c r="I53" t="n">
-        <v>40.5</v>
+        <v>97449.75</v>
       </c>
       <c r="J53" t="n">
-        <v>111</v>
-      </c>
-      <c r="K53" t="n">
-        <v>97449.75</v>
-      </c>
-      <c r="L53" t="n">
         <v>89280.5</v>
-      </c>
-      <c r="M53" t="n">
-        <v>11836.7998046875</v>
-      </c>
-      <c r="N53" t="n">
-        <v>11339.7998046875</v>
-      </c>
-      <c r="O53" t="n">
-        <v>10850.169921875</v>
-      </c>
-      <c r="P53" t="n">
-        <v>10400.08984375</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>44426.859375</v>
       </c>
     </row>
     <row r="54">
@@ -3513,40 +2386,19 @@
         <v>31716.26409451912</v>
       </c>
       <c r="F54" t="n">
-        <v>17984.16989753924</v>
+        <v>7036.5</v>
       </c>
       <c r="G54" t="n">
-        <v>13732.09419697988</v>
+        <v>24.5675</v>
       </c>
       <c r="H54" t="n">
-        <v>7036.5</v>
+        <v>255.75</v>
       </c>
       <c r="I54" t="n">
-        <v>24.5675</v>
+        <v>87876.75</v>
       </c>
       <c r="J54" t="n">
-        <v>255.75</v>
-      </c>
-      <c r="K54" t="n">
-        <v>87876.75</v>
-      </c>
-      <c r="L54" t="n">
         <v>2546</v>
-      </c>
-      <c r="M54" t="n">
-        <v>13732.08984375</v>
-      </c>
-      <c r="N54" t="n">
-        <v>13710.9404296875</v>
-      </c>
-      <c r="O54" t="n">
-        <v>14232.099609375</v>
-      </c>
-      <c r="P54" t="n">
-        <v>14590.4697265625</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>56265.599609375</v>
       </c>
     </row>
     <row r="55">
@@ -3570,40 +2422,19 @@
         <v>168847.9197490116</v>
       </c>
       <c r="F55" t="n">
-        <v>92622.38573350667</v>
+        <v>41823.75</v>
       </c>
       <c r="G55" t="n">
-        <v>76225.53401550491</v>
+        <v>191.975</v>
       </c>
       <c r="H55" t="n">
-        <v>41823.75</v>
+        <v>1299</v>
       </c>
       <c r="I55" t="n">
-        <v>191.975</v>
+        <v>541951</v>
       </c>
       <c r="J55" t="n">
-        <v>1299</v>
-      </c>
-      <c r="K55" t="n">
-        <v>541951</v>
-      </c>
-      <c r="L55" t="n">
         <v>245691.75</v>
-      </c>
-      <c r="M55" t="n">
-        <v>75830.5234375</v>
-      </c>
-      <c r="N55" t="n">
-        <v>78819.1171875</v>
-      </c>
-      <c r="O55" t="n">
-        <v>87271.6171875</v>
-      </c>
-      <c r="P55" t="n">
-        <v>88468.546875</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>330389.8046875</v>
       </c>
     </row>
     <row r="56">
@@ -3627,40 +2458,19 @@
         <v>35132.48182452414</v>
       </c>
       <c r="F56" t="n">
-        <v>19777.41245378139</v>
+        <v>10338.25</v>
       </c>
       <c r="G56" t="n">
-        <v>15355.06937074275</v>
+        <v>37.875</v>
       </c>
       <c r="H56" t="n">
-        <v>10338.25</v>
+        <v>339.25</v>
       </c>
       <c r="I56" t="n">
-        <v>37.875</v>
+        <v>127025.75</v>
       </c>
       <c r="J56" t="n">
-        <v>339.25</v>
-      </c>
-      <c r="K56" t="n">
-        <v>127025.75</v>
-      </c>
-      <c r="L56" t="n">
         <v>21419</v>
-      </c>
-      <c r="M56" t="n">
-        <v>15355.0703125</v>
-      </c>
-      <c r="N56" t="n">
-        <v>16076</v>
-      </c>
-      <c r="O56" t="n">
-        <v>15699.5498046875</v>
-      </c>
-      <c r="P56" t="n">
-        <v>15372.2099609375</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>62502.830078125</v>
       </c>
     </row>
     <row r="57">
@@ -3684,40 +2494,19 @@
         <v>94293.65917257563</v>
       </c>
       <c r="F57" t="n">
-        <v>46825.42631187108</v>
+        <v>15876.5</v>
       </c>
       <c r="G57" t="n">
-        <v>47468.23286070455</v>
+        <v>111</v>
       </c>
       <c r="H57" t="n">
-        <v>15876.5</v>
+        <v>751.75</v>
       </c>
       <c r="I57" t="n">
-        <v>111</v>
+        <v>251900</v>
       </c>
       <c r="J57" t="n">
-        <v>751.75</v>
-      </c>
-      <c r="K57" t="n">
-        <v>251900</v>
-      </c>
-      <c r="L57" t="n">
         <v>52605.25</v>
-      </c>
-      <c r="M57" t="n">
-        <v>47492.87890625</v>
-      </c>
-      <c r="N57" t="n">
-        <v>49784.48828125</v>
-      </c>
-      <c r="O57" t="n">
-        <v>50878.78125</v>
-      </c>
-      <c r="P57" t="n">
-        <v>54020.078125</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>202176.2265625</v>
       </c>
     </row>
     <row r="58">
@@ -3741,40 +2530,19 @@
         <v>13675.36303417142</v>
       </c>
       <c r="F58" t="n">
-        <v>7393.771889314319</v>
+        <v>2442.75</v>
       </c>
       <c r="G58" t="n">
-        <v>6281.591144857099</v>
+        <v>9.225000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>2442.75</v>
+        <v>178.75</v>
       </c>
       <c r="I58" t="n">
-        <v>9.225000000000001</v>
+        <v>28784</v>
       </c>
       <c r="J58" t="n">
-        <v>178.75</v>
-      </c>
-      <c r="K58" t="n">
-        <v>28784</v>
-      </c>
-      <c r="L58" t="n">
         <v>687.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>6281.58984375</v>
-      </c>
-      <c r="N58" t="n">
-        <v>6162.72998046875</v>
-      </c>
-      <c r="O58" t="n">
-        <v>6065.22021484375</v>
-      </c>
-      <c r="P58" t="n">
-        <v>5993.240234375</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>24502.7802734375</v>
       </c>
     </row>
     <row r="59">
@@ -3798,40 +2566,19 @@
         <v>64275.93059276438</v>
       </c>
       <c r="F59" t="n">
-        <v>33648.07242586771</v>
+        <v>12561.75</v>
       </c>
       <c r="G59" t="n">
-        <v>30627.85816689667</v>
+        <v>50</v>
       </c>
       <c r="H59" t="n">
-        <v>12561.75</v>
+        <v>465</v>
       </c>
       <c r="I59" t="n">
-        <v>50</v>
+        <v>172793</v>
       </c>
       <c r="J59" t="n">
-        <v>465</v>
-      </c>
-      <c r="K59" t="n">
-        <v>172793</v>
-      </c>
-      <c r="L59" t="n">
         <v>50806.75</v>
-      </c>
-      <c r="M59" t="n">
-        <v>30627.859375</v>
-      </c>
-      <c r="N59" t="n">
-        <v>30930.98046875</v>
-      </c>
-      <c r="O59" t="n">
-        <v>31036.359375</v>
-      </c>
-      <c r="P59" t="n">
-        <v>30927.560546875</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>123522.759765625</v>
       </c>
     </row>
     <row r="60">
@@ -3855,40 +2602,19 @@
         <v>61944.5293105305</v>
       </c>
       <c r="F60" t="n">
-        <v>34448.52171304182</v>
+        <v>22873.25</v>
       </c>
       <c r="G60" t="n">
-        <v>27496.00759748867</v>
+        <v>85.5</v>
       </c>
       <c r="H60" t="n">
-        <v>22873.25</v>
+        <v>207.5</v>
       </c>
       <c r="I60" t="n">
-        <v>85.5</v>
+        <v>271609.25</v>
       </c>
       <c r="J60" t="n">
-        <v>207.5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>271609.25</v>
-      </c>
-      <c r="L60" t="n">
         <v>145173.75</v>
-      </c>
-      <c r="M60" t="n">
-        <v>27496.009765625</v>
-      </c>
-      <c r="N60" t="n">
-        <v>28987.470703125</v>
-      </c>
-      <c r="O60" t="n">
-        <v>29737.970703125</v>
-      </c>
-      <c r="P60" t="n">
-        <v>30019.3203125</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>116240.771484375</v>
       </c>
     </row>
     <row r="61">
@@ -3912,40 +2638,19 @@
         <v>122854.9741160896</v>
       </c>
       <c r="F61" t="n">
-        <v>63285.19589916892</v>
+        <v>28778.5</v>
       </c>
       <c r="G61" t="n">
-        <v>59569.77821692068</v>
+        <v>137.75</v>
       </c>
       <c r="H61" t="n">
-        <v>28778.5</v>
+        <v>323.25</v>
       </c>
       <c r="I61" t="n">
-        <v>137.75</v>
+        <v>432432</v>
       </c>
       <c r="J61" t="n">
-        <v>323.25</v>
-      </c>
-      <c r="K61" t="n">
-        <v>432432</v>
-      </c>
-      <c r="L61" t="n">
         <v>68058</v>
-      </c>
-      <c r="M61" t="n">
-        <v>59583.5390625</v>
-      </c>
-      <c r="N61" t="n">
-        <v>64662.390625</v>
-      </c>
-      <c r="O61" t="n">
-        <v>70160.71875</v>
-      </c>
-      <c r="P61" t="n">
-        <v>73548.3984375</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>267955.046875</v>
       </c>
     </row>
     <row r="62">
@@ -3969,40 +2674,19 @@
         <v>62607.70477535234</v>
       </c>
       <c r="F62" t="n">
-        <v>34679.52629991269</v>
+        <v>17022.75</v>
       </c>
       <c r="G62" t="n">
-        <v>27928.17847543962</v>
+        <v>64.5</v>
       </c>
       <c r="H62" t="n">
-        <v>17022.75</v>
+        <v>499</v>
       </c>
       <c r="I62" t="n">
-        <v>64.5</v>
+        <v>259558</v>
       </c>
       <c r="J62" t="n">
-        <v>499</v>
-      </c>
-      <c r="K62" t="n">
-        <v>259558</v>
-      </c>
-      <c r="L62" t="n">
         <v>10925</v>
-      </c>
-      <c r="M62" t="n">
-        <v>27928.1796875</v>
-      </c>
-      <c r="N62" t="n">
-        <v>28530.3203125</v>
-      </c>
-      <c r="O62" t="n">
-        <v>27354.94921875</v>
-      </c>
-      <c r="P62" t="n">
-        <v>26252.859375</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>110066.30859375</v>
       </c>
     </row>
     <row r="63">
@@ -4026,40 +2710,19 @@
         <v>12379.48339545575</v>
       </c>
       <c r="F63" t="n">
-        <v>6400.225818468936</v>
+        <v>2657.75</v>
       </c>
       <c r="G63" t="n">
-        <v>5979.257576986815</v>
+        <v>13.8</v>
       </c>
       <c r="H63" t="n">
-        <v>2657.75</v>
+        <v>191.25</v>
       </c>
       <c r="I63" t="n">
-        <v>13.8</v>
+        <v>41402.25</v>
       </c>
       <c r="J63" t="n">
-        <v>191.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>41402.25</v>
-      </c>
-      <c r="L63" t="n">
         <v>18241.25</v>
-      </c>
-      <c r="M63" t="n">
-        <v>5979.259765625</v>
-      </c>
-      <c r="N63" t="n">
-        <v>5995.72021484375</v>
-      </c>
-      <c r="O63" t="n">
-        <v>6012.080078125</v>
-      </c>
-      <c r="P63" t="n">
-        <v>6021.08984375</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>24008.14990234375</v>
       </c>
     </row>
     <row r="64">
@@ -4083,40 +2746,19 @@
         <v>31718.16464135904</v>
       </c>
       <c r="F64" t="n">
-        <v>19151.76783382546</v>
+        <v>8684.75</v>
       </c>
       <c r="G64" t="n">
-        <v>12566.39680753357</v>
+        <v>37.325</v>
       </c>
       <c r="H64" t="n">
-        <v>8684.75</v>
+        <v>217</v>
       </c>
       <c r="I64" t="n">
-        <v>37.325</v>
+        <v>87093.25</v>
       </c>
       <c r="J64" t="n">
-        <v>217</v>
-      </c>
-      <c r="K64" t="n">
-        <v>87093.25</v>
-      </c>
-      <c r="L64" t="n">
         <v>80190.75</v>
-      </c>
-      <c r="M64" t="n">
-        <v>12566.400390625</v>
-      </c>
-      <c r="N64" t="n">
-        <v>12676.400390625</v>
-      </c>
-      <c r="O64" t="n">
-        <v>12452.5498046875</v>
-      </c>
-      <c r="P64" t="n">
-        <v>12381.5</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>50076.8505859375</v>
       </c>
     </row>
     <row r="65">
@@ -4140,40 +2782,19 @@
         <v>12611.42681325889</v>
       </c>
       <c r="F65" t="n">
-        <v>6495.26821117388</v>
+        <v>2460.25</v>
       </c>
       <c r="G65" t="n">
-        <v>6116.158602085015</v>
+        <v>15.1575</v>
       </c>
       <c r="H65" t="n">
-        <v>2460.25</v>
+        <v>130.25</v>
       </c>
       <c r="I65" t="n">
-        <v>15.1575</v>
+        <v>30931.5</v>
       </c>
       <c r="J65" t="n">
-        <v>130.25</v>
-      </c>
-      <c r="K65" t="n">
-        <v>30931.5</v>
-      </c>
-      <c r="L65" t="n">
         <v>11332.5</v>
-      </c>
-      <c r="M65" t="n">
-        <v>6116.16015625</v>
-      </c>
-      <c r="N65" t="n">
-        <v>6004.81982421875</v>
-      </c>
-      <c r="O65" t="n">
-        <v>5900.02978515625</v>
-      </c>
-      <c r="P65" t="n">
-        <v>5815.35986328125</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>23836.36962890625</v>
       </c>
     </row>
     <row r="66">
@@ -4197,40 +2818,19 @@
         <v>29008.8527278083</v>
       </c>
       <c r="F66" t="n">
-        <v>18316.69728162493</v>
+        <v>9768.25</v>
       </c>
       <c r="G66" t="n">
-        <v>10692.15544618336</v>
+        <v>37.75</v>
       </c>
       <c r="H66" t="n">
-        <v>9768.25</v>
+        <v>102.25</v>
       </c>
       <c r="I66" t="n">
-        <v>37.75</v>
+        <v>107426.25</v>
       </c>
       <c r="J66" t="n">
-        <v>102.25</v>
-      </c>
-      <c r="K66" t="n">
-        <v>107426.25</v>
-      </c>
-      <c r="L66" t="n">
         <v>50956.75</v>
-      </c>
-      <c r="M66" t="n">
-        <v>10692.16015625</v>
-      </c>
-      <c r="N66" t="n">
-        <v>11456.66015625</v>
-      </c>
-      <c r="O66" t="n">
-        <v>12019.3701171875</v>
-      </c>
-      <c r="P66" t="n">
-        <v>12419.7802734375</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>46587.970703125</v>
       </c>
     </row>
     <row r="67">
@@ -4254,40 +2854,19 @@
         <v>79941.61293859553</v>
       </c>
       <c r="F67" t="n">
-        <v>39942.78210257547</v>
+        <v>13561.5</v>
       </c>
       <c r="G67" t="n">
-        <v>39998.83083602006</v>
+        <v>80</v>
       </c>
       <c r="H67" t="n">
-        <v>13561.5</v>
+        <v>728.25</v>
       </c>
       <c r="I67" t="n">
-        <v>80</v>
+        <v>170283.75</v>
       </c>
       <c r="J67" t="n">
-        <v>728.25</v>
-      </c>
-      <c r="K67" t="n">
-        <v>170283.75</v>
-      </c>
-      <c r="L67" t="n">
         <v>154777.5</v>
-      </c>
-      <c r="M67" t="n">
-        <v>40227.671875</v>
-      </c>
-      <c r="N67" t="n">
-        <v>39791.421875</v>
-      </c>
-      <c r="O67" t="n">
-        <v>39697.578125</v>
-      </c>
-      <c r="P67" t="n">
-        <v>39718.01953125</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>159434.69140625</v>
       </c>
     </row>
     <row r="68">
@@ -4311,40 +2890,19 @@
         <v>10060.4490001577</v>
       </c>
       <c r="F68" t="n">
-        <v>5199.338391885941</v>
+        <v>1789.25</v>
       </c>
       <c r="G68" t="n">
-        <v>4861.11060827176</v>
+        <v>5</v>
       </c>
       <c r="H68" t="n">
-        <v>1789.25</v>
+        <v>87</v>
       </c>
       <c r="I68" t="n">
-        <v>5</v>
+        <v>17291.75</v>
       </c>
       <c r="J68" t="n">
-        <v>87</v>
-      </c>
-      <c r="K68" t="n">
-        <v>17291.75</v>
-      </c>
-      <c r="L68" t="n">
         <v>1672.5</v>
-      </c>
-      <c r="M68" t="n">
-        <v>4861.10986328125</v>
-      </c>
-      <c r="N68" t="n">
-        <v>4734.85009765625</v>
-      </c>
-      <c r="O68" t="n">
-        <v>4633.509765625</v>
-      </c>
-      <c r="P68" t="n">
-        <v>4580.52001953125</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>18809.98974609375</v>
       </c>
     </row>
     <row r="69">
@@ -4368,40 +2926,19 @@
         <v>42155.45526313809</v>
       </c>
       <c r="F69" t="n">
-        <v>24039.67911945938</v>
+        <v>12302.75</v>
       </c>
       <c r="G69" t="n">
-        <v>18115.7761436787</v>
+        <v>58</v>
       </c>
       <c r="H69" t="n">
-        <v>12302.75</v>
+        <v>266.25</v>
       </c>
       <c r="I69" t="n">
-        <v>58</v>
+        <v>132918.5</v>
       </c>
       <c r="J69" t="n">
-        <v>266.25</v>
-      </c>
-      <c r="K69" t="n">
-        <v>132918.5</v>
-      </c>
-      <c r="L69" t="n">
         <v>123673.25</v>
-      </c>
-      <c r="M69" t="n">
-        <v>18115.779296875</v>
-      </c>
-      <c r="N69" t="n">
-        <v>18100.359375</v>
-      </c>
-      <c r="O69" t="n">
-        <v>18547.5703125</v>
-      </c>
-      <c r="P69" t="n">
-        <v>19447.630859375</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>74211.33984375</v>
       </c>
     </row>
     <row r="70">
@@ -4425,40 +2962,19 @@
         <v>17866.66944096163</v>
       </c>
       <c r="F70" t="n">
-        <v>10955.17673402493</v>
+        <v>7318.25</v>
       </c>
       <c r="G70" t="n">
-        <v>6911.492706936696</v>
+        <v>15.375</v>
       </c>
       <c r="H70" t="n">
-        <v>7318.25</v>
+        <v>92</v>
       </c>
       <c r="I70" t="n">
-        <v>15.375</v>
+        <v>62748.5</v>
       </c>
       <c r="J70" t="n">
-        <v>92</v>
-      </c>
-      <c r="K70" t="n">
-        <v>62748.5</v>
-      </c>
-      <c r="L70" t="n">
         <v>612.75</v>
-      </c>
-      <c r="M70" t="n">
-        <v>6911.490234375</v>
-      </c>
-      <c r="N70" t="n">
-        <v>6801.5498046875</v>
-      </c>
-      <c r="O70" t="n">
-        <v>6570.35009765625</v>
-      </c>
-      <c r="P70" t="n">
-        <v>6367.669921875</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>26651.06005859375</v>
       </c>
     </row>
     <row r="71">
@@ -4482,40 +2998,19 @@
         <v>54683.09131437753</v>
       </c>
       <c r="F71" t="n">
-        <v>28018.30634148409</v>
+        <v>15397.25</v>
       </c>
       <c r="G71" t="n">
-        <v>26664.78497289344</v>
+        <v>51.8825</v>
       </c>
       <c r="H71" t="n">
-        <v>15397.25</v>
+        <v>172.5</v>
       </c>
       <c r="I71" t="n">
-        <v>51.8825</v>
+        <v>197977.25</v>
       </c>
       <c r="J71" t="n">
-        <v>172.5</v>
-      </c>
-      <c r="K71" t="n">
-        <v>197977.25</v>
-      </c>
-      <c r="L71" t="n">
         <v>24340.5</v>
-      </c>
-      <c r="M71" t="n">
-        <v>26664.779296875</v>
-      </c>
-      <c r="N71" t="n">
-        <v>27258.560546875</v>
-      </c>
-      <c r="O71" t="n">
-        <v>26730.900390625</v>
-      </c>
-      <c r="P71" t="n">
-        <v>26180.55078125</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>106834.791015625</v>
       </c>
     </row>
     <row r="72">
@@ -4539,40 +3034,19 @@
         <v>107590.1845253756</v>
       </c>
       <c r="F72" t="n">
-        <v>58969.35493792914</v>
+        <v>23149.25</v>
       </c>
       <c r="G72" t="n">
-        <v>48620.82958744642</v>
+        <v>119.25</v>
       </c>
       <c r="H72" t="n">
-        <v>23149.25</v>
+        <v>1101</v>
       </c>
       <c r="I72" t="n">
-        <v>119.25</v>
+        <v>397595.75</v>
       </c>
       <c r="J72" t="n">
-        <v>1101</v>
-      </c>
-      <c r="K72" t="n">
-        <v>397595.75</v>
-      </c>
-      <c r="L72" t="n">
         <v>81571.75</v>
-      </c>
-      <c r="M72" t="n">
-        <v>48620.828125</v>
-      </c>
-      <c r="N72" t="n">
-        <v>47904.0390625</v>
-      </c>
-      <c r="O72" t="n">
-        <v>46972.62109375</v>
-      </c>
-      <c r="P72" t="n">
-        <v>46367.69921875</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>189865.1875</v>
       </c>
     </row>
     <row r="73">
@@ -4596,40 +3070,19 @@
         <v>57646.33597912685</v>
       </c>
       <c r="F73" t="n">
-        <v>29795.48957508342</v>
+        <v>12155.5</v>
       </c>
       <c r="G73" t="n">
-        <v>27850.84640404343</v>
+        <v>60.25</v>
       </c>
       <c r="H73" t="n">
-        <v>12155.5</v>
+        <v>226.75</v>
       </c>
       <c r="I73" t="n">
-        <v>60.25</v>
+        <v>142328</v>
       </c>
       <c r="J73" t="n">
-        <v>226.75</v>
-      </c>
-      <c r="K73" t="n">
-        <v>142328</v>
-      </c>
-      <c r="L73" t="n">
         <v>121132.5</v>
-      </c>
-      <c r="M73" t="n">
-        <v>27844.140625</v>
-      </c>
-      <c r="N73" t="n">
-        <v>29487.0390625</v>
-      </c>
-      <c r="O73" t="n">
-        <v>29198.630859375</v>
-      </c>
-      <c r="P73" t="n">
-        <v>28561.859375</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>115091.669921875</v>
       </c>
     </row>
     <row r="74">
@@ -4653,40 +3106,19 @@
         <v>25799.4185199124</v>
       </c>
       <c r="F74" t="n">
-        <v>14541.99089287555</v>
+        <v>4221.25</v>
       </c>
       <c r="G74" t="n">
-        <v>11257.42762703685</v>
+        <v>17</v>
       </c>
       <c r="H74" t="n">
-        <v>4221.25</v>
+        <v>237.25</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>50629.25</v>
       </c>
       <c r="J74" t="n">
-        <v>237.25</v>
-      </c>
-      <c r="K74" t="n">
-        <v>50629.25</v>
-      </c>
-      <c r="L74" t="n">
         <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>11257.4296875</v>
-      </c>
-      <c r="N74" t="n">
-        <v>10956.099609375</v>
-      </c>
-      <c r="O74" t="n">
-        <v>10403.509765625</v>
-      </c>
-      <c r="P74" t="n">
-        <v>9850.4599609375</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>42467.4990234375</v>
       </c>
     </row>
     <row r="75">
@@ -4710,40 +3142,19 @@
         <v>44817.88634177817</v>
       </c>
       <c r="F75" t="n">
-        <v>26140.85968294419</v>
+        <v>13806.25</v>
       </c>
       <c r="G75" t="n">
-        <v>18677.02665883398</v>
+        <v>47</v>
       </c>
       <c r="H75" t="n">
-        <v>13806.25</v>
+        <v>522.25</v>
       </c>
       <c r="I75" t="n">
-        <v>47</v>
+        <v>164146.5</v>
       </c>
       <c r="J75" t="n">
-        <v>522.25</v>
-      </c>
-      <c r="K75" t="n">
-        <v>164146.5</v>
-      </c>
-      <c r="L75" t="n">
         <v>33995.75</v>
-      </c>
-      <c r="M75" t="n">
-        <v>18677.029296875</v>
-      </c>
-      <c r="N75" t="n">
-        <v>18244.380859375</v>
-      </c>
-      <c r="O75" t="n">
-        <v>17808.5</v>
-      </c>
-      <c r="P75" t="n">
-        <v>17395.91015625</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>72125.8203125</v>
       </c>
     </row>
     <row r="76">
@@ -4767,40 +3178,19 @@
         <v>12063.17468929075</v>
       </c>
       <c r="F76" t="n">
-        <v>6949.241634788606</v>
+        <v>3556.5</v>
       </c>
       <c r="G76" t="n">
-        <v>5113.933054502143</v>
+        <v>16.7425</v>
       </c>
       <c r="H76" t="n">
-        <v>3556.5</v>
+        <v>81.25</v>
       </c>
       <c r="I76" t="n">
-        <v>16.7425</v>
+        <v>54726.75</v>
       </c>
       <c r="J76" t="n">
-        <v>81.25</v>
-      </c>
-      <c r="K76" t="n">
-        <v>54726.75</v>
-      </c>
-      <c r="L76" t="n">
         <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>5113.93017578125</v>
-      </c>
-      <c r="N76" t="n">
-        <v>5104.72998046875</v>
-      </c>
-      <c r="O76" t="n">
-        <v>5119.9599609375</v>
-      </c>
-      <c r="P76" t="n">
-        <v>5124.0498046875</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>20462.669921875</v>
       </c>
     </row>
     <row r="77">
@@ -4824,40 +3214,19 @@
         <v>94932.54745284264</v>
       </c>
       <c r="F77" t="n">
-        <v>46110.48032496547</v>
+        <v>17786.75</v>
       </c>
       <c r="G77" t="n">
-        <v>48822.06712787718</v>
+        <v>77</v>
       </c>
       <c r="H77" t="n">
-        <v>17786.75</v>
+        <v>603.75</v>
       </c>
       <c r="I77" t="n">
-        <v>77</v>
+        <v>229459.75</v>
       </c>
       <c r="J77" t="n">
-        <v>603.75</v>
-      </c>
-      <c r="K77" t="n">
-        <v>229459.75</v>
-      </c>
-      <c r="L77" t="n">
         <v>75519</v>
-      </c>
-      <c r="M77" t="n">
-        <v>48822.05859375</v>
-      </c>
-      <c r="N77" t="n">
-        <v>53701.23828125</v>
-      </c>
-      <c r="O77" t="n">
-        <v>63863.23828125</v>
-      </c>
-      <c r="P77" t="n">
-        <v>69088.1484375</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>235474.68359375</v>
       </c>
     </row>
     <row r="78">
@@ -4881,40 +3250,19 @@
         <v>15316.63387352338</v>
       </c>
       <c r="F78" t="n">
-        <v>7996.337488809383</v>
+        <v>2859</v>
       </c>
       <c r="G78" t="n">
-        <v>7320.296384713994</v>
+        <v>12.4575</v>
       </c>
       <c r="H78" t="n">
-        <v>2859</v>
+        <v>149.75</v>
       </c>
       <c r="I78" t="n">
-        <v>12.4575</v>
+        <v>39596.75</v>
       </c>
       <c r="J78" t="n">
-        <v>149.75</v>
-      </c>
-      <c r="K78" t="n">
-        <v>39596.75</v>
-      </c>
-      <c r="L78" t="n">
         <v>50.75</v>
-      </c>
-      <c r="M78" t="n">
-        <v>7320.2998046875</v>
-      </c>
-      <c r="N78" t="n">
-        <v>7322.64013671875</v>
-      </c>
-      <c r="O78" t="n">
-        <v>7253.77978515625</v>
-      </c>
-      <c r="P78" t="n">
-        <v>7350.7099609375</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>29247.4296875</v>
       </c>
     </row>
     <row r="79">
@@ -4938,40 +3286,19 @@
         <v>41596.0493520079</v>
       </c>
       <c r="F79" t="n">
-        <v>21153.56935772676</v>
+        <v>7926</v>
       </c>
       <c r="G79" t="n">
-        <v>20442.47999428115</v>
+        <v>35.695</v>
       </c>
       <c r="H79" t="n">
-        <v>7926</v>
+        <v>358</v>
       </c>
       <c r="I79" t="n">
-        <v>35.695</v>
+        <v>122885.5</v>
       </c>
       <c r="J79" t="n">
-        <v>358</v>
-      </c>
-      <c r="K79" t="n">
-        <v>122885.5</v>
-      </c>
-      <c r="L79" t="n">
         <v>2056.25</v>
-      </c>
-      <c r="M79" t="n">
-        <v>20442.48046875</v>
-      </c>
-      <c r="N79" t="n">
-        <v>20498.279296875</v>
-      </c>
-      <c r="O79" t="n">
-        <v>20306.810546875</v>
-      </c>
-      <c r="P79" t="n">
-        <v>20099.80078125</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>81347.37109375</v>
       </c>
     </row>
     <row r="80">
@@ -4995,40 +3322,19 @@
         <v>15128.66342863071</v>
       </c>
       <c r="F80" t="n">
-        <v>8398.795311745935</v>
+        <v>3997.75</v>
       </c>
       <c r="G80" t="n">
-        <v>6729.868116884777</v>
+        <v>17.525</v>
       </c>
       <c r="H80" t="n">
-        <v>3997.75</v>
+        <v>50</v>
       </c>
       <c r="I80" t="n">
-        <v>17.525</v>
+        <v>58946.5</v>
       </c>
       <c r="J80" t="n">
-        <v>50</v>
-      </c>
-      <c r="K80" t="n">
-        <v>58946.5</v>
-      </c>
-      <c r="L80" t="n">
         <v>6385.25</v>
-      </c>
-      <c r="M80" t="n">
-        <v>6726.3701171875</v>
-      </c>
-      <c r="N80" t="n">
-        <v>6645.169921875</v>
-      </c>
-      <c r="O80" t="n">
-        <v>6575.68994140625</v>
-      </c>
-      <c r="P80" t="n">
-        <v>6505.97998046875</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>26453.2099609375</v>
       </c>
     </row>
     <row r="81">
@@ -5052,40 +3358,19 @@
         <v>8016.518554017678</v>
       </c>
       <c r="F81" t="n">
-        <v>4394.027753129965</v>
+        <v>1341.5</v>
       </c>
       <c r="G81" t="n">
-        <v>3622.490800887713</v>
+        <v>5</v>
       </c>
       <c r="H81" t="n">
-        <v>1341.5</v>
+        <v>154.75</v>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>13825</v>
       </c>
       <c r="J81" t="n">
-        <v>154.75</v>
-      </c>
-      <c r="K81" t="n">
-        <v>13825</v>
-      </c>
-      <c r="L81" t="n">
         <v>2988.25</v>
-      </c>
-      <c r="M81" t="n">
-        <v>3622.489990234375</v>
-      </c>
-      <c r="N81" t="n">
-        <v>3516.469970703125</v>
-      </c>
-      <c r="O81" t="n">
-        <v>3418.5</v>
-      </c>
-      <c r="P81" t="n">
-        <v>3377.43994140625</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>13934.89990234375</v>
       </c>
     </row>
     <row r="82">
@@ -5109,40 +3394,19 @@
         <v>79932.58685717691</v>
       </c>
       <c r="F82" t="n">
-        <v>45240.04536033788</v>
+        <v>18974.5</v>
       </c>
       <c r="G82" t="n">
-        <v>34692.541496839</v>
+        <v>92</v>
       </c>
       <c r="H82" t="n">
-        <v>18974.5</v>
+        <v>618</v>
       </c>
       <c r="I82" t="n">
-        <v>92</v>
+        <v>258650</v>
       </c>
       <c r="J82" t="n">
-        <v>618</v>
-      </c>
-      <c r="K82" t="n">
-        <v>258650</v>
-      </c>
-      <c r="L82" t="n">
         <v>65132.75</v>
-      </c>
-      <c r="M82" t="n">
-        <v>34692.5390625</v>
-      </c>
-      <c r="N82" t="n">
-        <v>34516.01171875</v>
-      </c>
-      <c r="O82" t="n">
-        <v>35543.4296875</v>
-      </c>
-      <c r="P82" t="n">
-        <v>36279.26171875</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>141031.2421875</v>
       </c>
     </row>
     <row r="83">
@@ -5166,40 +3430,19 @@
         <v>68073.84812772916</v>
       </c>
       <c r="F83" t="n">
-        <v>38223.71762873957</v>
+        <v>20813.75</v>
       </c>
       <c r="G83" t="n">
-        <v>29850.13049898959</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>20813.75</v>
+        <v>192.5</v>
       </c>
       <c r="I83" t="n">
-        <v>77.40000000000001</v>
+        <v>237968.25</v>
       </c>
       <c r="J83" t="n">
-        <v>192.5</v>
-      </c>
-      <c r="K83" t="n">
-        <v>237968.25</v>
-      </c>
-      <c r="L83" t="n">
         <v>76007.25</v>
-      </c>
-      <c r="M83" t="n">
-        <v>29850.130859375</v>
-      </c>
-      <c r="N83" t="n">
-        <v>30102.330078125</v>
-      </c>
-      <c r="O83" t="n">
-        <v>30490.3203125</v>
-      </c>
-      <c r="P83" t="n">
-        <v>30696.310546875</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>121139.091796875</v>
       </c>
     </row>
     <row r="84">
@@ -5223,40 +3466,19 @@
         <v>11999.34698301016</v>
       </c>
       <c r="F84" t="n">
-        <v>7788.003410247657</v>
+        <v>3541</v>
       </c>
       <c r="G84" t="n">
-        <v>4211.343572762506</v>
+        <v>12.75</v>
       </c>
       <c r="H84" t="n">
-        <v>3541</v>
+        <v>72.25</v>
       </c>
       <c r="I84" t="n">
-        <v>12.75</v>
+        <v>45654.25</v>
       </c>
       <c r="J84" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="K84" t="n">
-        <v>45654.25</v>
-      </c>
-      <c r="L84" t="n">
         <v>9953.75</v>
-      </c>
-      <c r="M84" t="n">
-        <v>4211.33984375</v>
-      </c>
-      <c r="N84" t="n">
-        <v>4101.89013671875</v>
-      </c>
-      <c r="O84" t="n">
-        <v>3970.75</v>
-      </c>
-      <c r="P84" t="n">
-        <v>3739</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>16022.97998046875</v>
       </c>
     </row>
     <row r="85">
@@ -5280,40 +3502,19 @@
         <v>91004.97199041263</v>
       </c>
       <c r="F85" t="n">
-        <v>51034.47427960932</v>
+        <v>29213.25</v>
       </c>
       <c r="G85" t="n">
-        <v>39970.49771080329</v>
+        <v>118</v>
       </c>
       <c r="H85" t="n">
-        <v>29213.25</v>
+        <v>255.5</v>
       </c>
       <c r="I85" t="n">
-        <v>118</v>
+        <v>414720.75</v>
       </c>
       <c r="J85" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="K85" t="n">
-        <v>414720.75</v>
-      </c>
-      <c r="L85" t="n">
         <v>58506.5</v>
-      </c>
-      <c r="M85" t="n">
-        <v>39970.5</v>
-      </c>
-      <c r="N85" t="n">
-        <v>38031.26953125</v>
-      </c>
-      <c r="O85" t="n">
-        <v>36170.421875</v>
-      </c>
-      <c r="P85" t="n">
-        <v>34389.5</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>148561.69140625</v>
       </c>
     </row>
     <row r="86">
@@ -5337,40 +3538,19 @@
         <v>44256.29179743752</v>
       </c>
       <c r="F86" t="n">
-        <v>22620.6934072848</v>
+        <v>7632.5</v>
       </c>
       <c r="G86" t="n">
-        <v>21635.59839015271</v>
+        <v>40</v>
       </c>
       <c r="H86" t="n">
-        <v>7632.5</v>
+        <v>199.5</v>
       </c>
       <c r="I86" t="n">
-        <v>40</v>
+        <v>132392.5</v>
       </c>
       <c r="J86" t="n">
-        <v>199.5</v>
-      </c>
-      <c r="K86" t="n">
-        <v>132392.5</v>
-      </c>
-      <c r="L86" t="n">
         <v>15551.75</v>
-      </c>
-      <c r="M86" t="n">
-        <v>21602.75</v>
-      </c>
-      <c r="N86" t="n">
-        <v>23615.970703125</v>
-      </c>
-      <c r="O86" t="n">
-        <v>24251.990234375</v>
-      </c>
-      <c r="P86" t="n">
-        <v>24262.5390625</v>
-      </c>
-      <c r="Q86" t="n">
-        <v>93733.25</v>
       </c>
     </row>
     <row r="87">
@@ -5394,40 +3574,19 @@
         <v>1477.157581738303</v>
       </c>
       <c r="F87" t="n">
-        <v>649.4678736825205</v>
+        <v>236.25</v>
       </c>
       <c r="G87" t="n">
-        <v>827.6897080557827</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>236.25</v>
+        <v>21.5</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>2551.5</v>
       </c>
       <c r="J87" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="K87" t="n">
-        <v>2551.5</v>
-      </c>
-      <c r="L87" t="n">
         <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>827.6900024414062</v>
-      </c>
-      <c r="N87" t="n">
-        <v>846.5599975585938</v>
-      </c>
-      <c r="O87" t="n">
-        <v>879.4600219726562</v>
-      </c>
-      <c r="P87" t="n">
-        <v>847.8499755859375</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>3401.559997558594</v>
       </c>
     </row>
     <row r="88">
@@ -5451,40 +3610,19 @@
         <v>121124.4156857012</v>
       </c>
       <c r="F88" t="n">
-        <v>65819.15546469112</v>
+        <v>28102.25</v>
       </c>
       <c r="G88" t="n">
-        <v>55305.26022101007</v>
+        <v>145.45</v>
       </c>
       <c r="H88" t="n">
-        <v>28102.25</v>
+        <v>514</v>
       </c>
       <c r="I88" t="n">
-        <v>145.45</v>
+        <v>451495.75</v>
       </c>
       <c r="J88" t="n">
-        <v>514</v>
-      </c>
-      <c r="K88" t="n">
-        <v>451495.75</v>
-      </c>
-      <c r="L88" t="n">
         <v>141004.5</v>
-      </c>
-      <c r="M88" t="n">
-        <v>53756.69140625</v>
-      </c>
-      <c r="N88" t="n">
-        <v>53278.3515625</v>
-      </c>
-      <c r="O88" t="n">
-        <v>57247.78125</v>
-      </c>
-      <c r="P88" t="n">
-        <v>59122.51171875</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>223405.3359375</v>
       </c>
     </row>
     <row r="89">
@@ -5508,40 +3646,19 @@
         <v>16141.61181219503</v>
       </c>
       <c r="F89" t="n">
-        <v>8859.550181141845</v>
+        <v>3506.25</v>
       </c>
       <c r="G89" t="n">
-        <v>7282.061631053178</v>
+        <v>18.5</v>
       </c>
       <c r="H89" t="n">
-        <v>3506.25</v>
+        <v>123.75</v>
       </c>
       <c r="I89" t="n">
-        <v>18.5</v>
+        <v>52995</v>
       </c>
       <c r="J89" t="n">
-        <v>123.75</v>
-      </c>
-      <c r="K89" t="n">
-        <v>52995</v>
-      </c>
-      <c r="L89" t="n">
         <v>14726.25</v>
-      </c>
-      <c r="M89" t="n">
-        <v>7282.06005859375</v>
-      </c>
-      <c r="N89" t="n">
-        <v>6935.2900390625</v>
-      </c>
-      <c r="O89" t="n">
-        <v>6594.0400390625</v>
-      </c>
-      <c r="P89" t="n">
-        <v>6267.43017578125</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>27078.8203125</v>
       </c>
     </row>
     <row r="90">
@@ -5565,40 +3682,19 @@
         <v>35209.07745494865</v>
       </c>
       <c r="F90" t="n">
-        <v>20337.61021651287</v>
+        <v>9297.5</v>
       </c>
       <c r="G90" t="n">
-        <v>14871.46723843578</v>
+        <v>34</v>
       </c>
       <c r="H90" t="n">
-        <v>9297.5</v>
+        <v>199</v>
       </c>
       <c r="I90" t="n">
-        <v>34</v>
+        <v>104162.5</v>
       </c>
       <c r="J90" t="n">
-        <v>199</v>
-      </c>
-      <c r="K90" t="n">
-        <v>104162.5</v>
-      </c>
-      <c r="L90" t="n">
         <v>24612.75</v>
-      </c>
-      <c r="M90" t="n">
-        <v>14871.4697265625</v>
-      </c>
-      <c r="N90" t="n">
-        <v>14811.1103515625</v>
-      </c>
-      <c r="O90" t="n">
-        <v>14776.0302734375</v>
-      </c>
-      <c r="P90" t="n">
-        <v>14769.0498046875</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>59227.66015625</v>
       </c>
     </row>
     <row r="91">
@@ -5622,40 +3718,19 @@
         <v>119335.4082425264</v>
       </c>
       <c r="F91" t="n">
-        <v>65067.13202784144</v>
+        <v>20591.5</v>
       </c>
       <c r="G91" t="n">
-        <v>54268.27621468501</v>
+        <v>89.375</v>
       </c>
       <c r="H91" t="n">
-        <v>20591.5</v>
+        <v>869.25</v>
       </c>
       <c r="I91" t="n">
-        <v>89.375</v>
+        <v>291081</v>
       </c>
       <c r="J91" t="n">
-        <v>869.25</v>
-      </c>
-      <c r="K91" t="n">
-        <v>291081</v>
-      </c>
-      <c r="L91" t="n">
         <v>35235.75</v>
-      </c>
-      <c r="M91" t="n">
-        <v>54268.28125</v>
-      </c>
-      <c r="N91" t="n">
-        <v>54051.30078125</v>
-      </c>
-      <c r="O91" t="n">
-        <v>53710.28125</v>
-      </c>
-      <c r="P91" t="n">
-        <v>53693.921875</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>215723.78515625</v>
       </c>
     </row>
     <row r="92">
@@ -5679,40 +3754,19 @@
         <v>22088.15324538365</v>
       </c>
       <c r="F92" t="n">
-        <v>12325.66974976067</v>
+        <v>5685.25</v>
       </c>
       <c r="G92" t="n">
-        <v>9762.483495622972</v>
+        <v>21.475</v>
       </c>
       <c r="H92" t="n">
-        <v>5685.25</v>
+        <v>90.25</v>
       </c>
       <c r="I92" t="n">
-        <v>21.475</v>
+        <v>67533.5</v>
       </c>
       <c r="J92" t="n">
-        <v>90.25</v>
-      </c>
-      <c r="K92" t="n">
-        <v>67533.5</v>
-      </c>
-      <c r="L92" t="n">
         <v>12081.5</v>
-      </c>
-      <c r="M92" t="n">
-        <v>9762.48046875</v>
-      </c>
-      <c r="N92" t="n">
-        <v>9868.759765625</v>
-      </c>
-      <c r="O92" t="n">
-        <v>10575.1201171875</v>
-      </c>
-      <c r="P92" t="n">
-        <v>10165.419921875</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>40371.7802734375</v>
       </c>
     </row>
     <row r="93">
@@ -5736,40 +3790,19 @@
         <v>178188.885590083</v>
       </c>
       <c r="F93" t="n">
-        <v>92092.07913150187</v>
+        <v>53262</v>
       </c>
       <c r="G93" t="n">
-        <v>86096.80645858109</v>
+        <v>209.915</v>
       </c>
       <c r="H93" t="n">
-        <v>53262</v>
+        <v>1083</v>
       </c>
       <c r="I93" t="n">
-        <v>209.915</v>
+        <v>648425.75</v>
       </c>
       <c r="J93" t="n">
-        <v>1083</v>
-      </c>
-      <c r="K93" t="n">
-        <v>648425.75</v>
-      </c>
-      <c r="L93" t="n">
         <v>326483.5</v>
-      </c>
-      <c r="M93" t="n">
-        <v>86155.2265625</v>
-      </c>
-      <c r="N93" t="n">
-        <v>91858.28125</v>
-      </c>
-      <c r="O93" t="n">
-        <v>96743.59375</v>
-      </c>
-      <c r="P93" t="n">
-        <v>101539.5078125</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>376296.609375</v>
       </c>
     </row>
     <row r="94">
@@ -5793,40 +3826,19 @@
         <v>22257.89700914234</v>
       </c>
       <c r="F94" t="n">
-        <v>13493.25906050424</v>
+        <v>5374.75</v>
       </c>
       <c r="G94" t="n">
-        <v>8764.637948638097</v>
+        <v>23.45</v>
       </c>
       <c r="H94" t="n">
-        <v>5374.75</v>
+        <v>162.5</v>
       </c>
       <c r="I94" t="n">
-        <v>23.45</v>
+        <v>76234.75</v>
       </c>
       <c r="J94" t="n">
-        <v>162.5</v>
-      </c>
-      <c r="K94" t="n">
-        <v>76234.75</v>
-      </c>
-      <c r="L94" t="n">
         <v>15193.25</v>
-      </c>
-      <c r="M94" t="n">
-        <v>8808.7998046875</v>
-      </c>
-      <c r="N94" t="n">
-        <v>8870.330078125</v>
-      </c>
-      <c r="O94" t="n">
-        <v>10389.9404296875</v>
-      </c>
-      <c r="P94" t="n">
-        <v>11192.990234375</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>39262.060546875</v>
       </c>
     </row>
     <row r="95">
@@ -5850,40 +3862,19 @@
         <v>70912.59910782923</v>
       </c>
       <c r="F95" t="n">
-        <v>39509.71845502767</v>
+        <v>25001.5</v>
       </c>
       <c r="G95" t="n">
-        <v>31402.88065280156</v>
+        <v>85.09</v>
       </c>
       <c r="H95" t="n">
-        <v>25001.5</v>
+        <v>502.25</v>
       </c>
       <c r="I95" t="n">
-        <v>85.09</v>
+        <v>294932</v>
       </c>
       <c r="J95" t="n">
-        <v>502.25</v>
-      </c>
-      <c r="K95" t="n">
-        <v>294932</v>
-      </c>
-      <c r="L95" t="n">
         <v>68263.5</v>
-      </c>
-      <c r="M95" t="n">
-        <v>31402.880859375</v>
-      </c>
-      <c r="N95" t="n">
-        <v>31076.759765625</v>
-      </c>
-      <c r="O95" t="n">
-        <v>30320.16015625</v>
-      </c>
-      <c r="P95" t="n">
-        <v>34664.5</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>127464.30078125</v>
       </c>
     </row>
     <row r="96">
@@ -5907,40 +3898,19 @@
         <v>5151.206193579867</v>
       </c>
       <c r="F96" t="n">
-        <v>3053.526750220492</v>
+        <v>951.25</v>
       </c>
       <c r="G96" t="n">
-        <v>2097.679443359375</v>
+        <v>4.375</v>
       </c>
       <c r="H96" t="n">
-        <v>951.25</v>
+        <v>49.5</v>
       </c>
       <c r="I96" t="n">
-        <v>4.375</v>
+        <v>15144.5</v>
       </c>
       <c r="J96" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="K96" t="n">
-        <v>15144.5</v>
-      </c>
-      <c r="L96" t="n">
         <v>60.75</v>
-      </c>
-      <c r="M96" t="n">
-        <v>2097.679931640625</v>
-      </c>
-      <c r="N96" t="n">
-        <v>1993.06005859375</v>
-      </c>
-      <c r="O96" t="n">
-        <v>1904.2900390625</v>
-      </c>
-      <c r="P96" t="n">
-        <v>1854.510009765625</v>
-      </c>
-      <c r="Q96" t="n">
-        <v>7849.5400390625</v>
       </c>
     </row>
     <row r="97">
@@ -5964,40 +3934,19 @@
         <v>78567.97184101606</v>
       </c>
       <c r="F97" t="n">
-        <v>40465.34696819762</v>
+        <v>26477.75</v>
       </c>
       <c r="G97" t="n">
-        <v>38102.62487281843</v>
+        <v>92</v>
       </c>
       <c r="H97" t="n">
-        <v>26477.75</v>
+        <v>531.5</v>
       </c>
       <c r="I97" t="n">
-        <v>92</v>
+        <v>284044.25</v>
       </c>
       <c r="J97" t="n">
-        <v>531.5</v>
-      </c>
-      <c r="K97" t="n">
-        <v>284044.25</v>
-      </c>
-      <c r="L97" t="n">
         <v>75432.25</v>
-      </c>
-      <c r="M97" t="n">
-        <v>38102.62109375</v>
-      </c>
-      <c r="N97" t="n">
-        <v>41652.671875</v>
-      </c>
-      <c r="O97" t="n">
-        <v>42625.640625</v>
-      </c>
-      <c r="P97" t="n">
-        <v>41780.98828125</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>164161.921875</v>
       </c>
     </row>
     <row r="98">
@@ -6021,40 +3970,19 @@
         <v>15226.23800618228</v>
       </c>
       <c r="F98" t="n">
-        <v>8056.464969663099</v>
+        <v>2662.5</v>
       </c>
       <c r="G98" t="n">
-        <v>7169.773036519179</v>
+        <v>11.5</v>
       </c>
       <c r="H98" t="n">
-        <v>2662.5</v>
+        <v>209.5</v>
       </c>
       <c r="I98" t="n">
-        <v>11.5</v>
+        <v>37838.5</v>
       </c>
       <c r="J98" t="n">
-        <v>209.5</v>
-      </c>
-      <c r="K98" t="n">
-        <v>37838.5</v>
-      </c>
-      <c r="L98" t="n">
         <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>7169.77001953125</v>
-      </c>
-      <c r="N98" t="n">
-        <v>9309.48046875</v>
-      </c>
-      <c r="O98" t="n">
-        <v>11519.3603515625</v>
-      </c>
-      <c r="P98" t="n">
-        <v>11187.900390625</v>
-      </c>
-      <c r="Q98" t="n">
-        <v>39186.51123046875</v>
       </c>
     </row>
     <row r="99">
@@ -6078,40 +4006,19 @@
         <v>19305.43956735783</v>
       </c>
       <c r="F99" t="n">
-        <v>10733.21019129124</v>
+        <v>4510.25</v>
       </c>
       <c r="G99" t="n">
-        <v>8572.229376066587</v>
+        <v>20</v>
       </c>
       <c r="H99" t="n">
-        <v>4510.25</v>
+        <v>237</v>
       </c>
       <c r="I99" t="n">
-        <v>20</v>
+        <v>68144.25</v>
       </c>
       <c r="J99" t="n">
-        <v>237</v>
-      </c>
-      <c r="K99" t="n">
-        <v>68144.25</v>
-      </c>
-      <c r="L99" t="n">
         <v>14043.75</v>
-      </c>
-      <c r="M99" t="n">
-        <v>8572.41015625</v>
-      </c>
-      <c r="N99" t="n">
-        <v>8352.7197265625</v>
-      </c>
-      <c r="O99" t="n">
-        <v>8094.18994140625</v>
-      </c>
-      <c r="P99" t="n">
-        <v>8243.6796875</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>33262.99951171875</v>
       </c>
     </row>
     <row r="100">
@@ -6135,40 +4042,19 @@
         <v>79253.45174763906</v>
       </c>
       <c r="F100" t="n">
-        <v>45663.91975747922</v>
+        <v>23678</v>
       </c>
       <c r="G100" t="n">
-        <v>33589.53199015983</v>
+        <v>73.95499999999998</v>
       </c>
       <c r="H100" t="n">
-        <v>23678</v>
+        <v>348</v>
       </c>
       <c r="I100" t="n">
-        <v>73.95499999999998</v>
+        <v>295266.75</v>
       </c>
       <c r="J100" t="n">
-        <v>348</v>
-      </c>
-      <c r="K100" t="n">
-        <v>295266.75</v>
-      </c>
-      <c r="L100" t="n">
         <v>49306.25</v>
-      </c>
-      <c r="M100" t="n">
-        <v>34033.69140625</v>
-      </c>
-      <c r="N100" t="n">
-        <v>33402.7109375</v>
-      </c>
-      <c r="O100" t="n">
-        <v>32265.66015625</v>
-      </c>
-      <c r="P100" t="n">
-        <v>31251.580078125</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>130953.642578125</v>
       </c>
     </row>
     <row r="101">
@@ -6192,40 +4078,19 @@
         <v>75955.01866052406</v>
       </c>
       <c r="F101" t="n">
-        <v>37432.45817459693</v>
+        <v>11399.5</v>
       </c>
       <c r="G101" t="n">
-        <v>38522.56048592714</v>
+        <v>49.2</v>
       </c>
       <c r="H101" t="n">
-        <v>11399.5</v>
+        <v>753.5</v>
       </c>
       <c r="I101" t="n">
-        <v>49.2</v>
+        <v>165839.75</v>
       </c>
       <c r="J101" t="n">
-        <v>753.5</v>
-      </c>
-      <c r="K101" t="n">
-        <v>165839.75</v>
-      </c>
-      <c r="L101" t="n">
         <v>36222</v>
-      </c>
-      <c r="M101" t="n">
-        <v>38522.55859375</v>
-      </c>
-      <c r="N101" t="n">
-        <v>38181.80078125</v>
-      </c>
-      <c r="O101" t="n">
-        <v>37785.73046875</v>
-      </c>
-      <c r="P101" t="n">
-        <v>37634.62890625</v>
-      </c>
-      <c r="Q101" t="n">
-        <v>152124.71875</v>
       </c>
     </row>
     <row r="102">
@@ -6249,40 +4114,19 @@
         <v>41591.21329882056</v>
       </c>
       <c r="F102" t="n">
-        <v>23802.32077797361</v>
+        <v>10672.5</v>
       </c>
       <c r="G102" t="n">
-        <v>17788.89252084695</v>
+        <v>53</v>
       </c>
       <c r="H102" t="n">
-        <v>10672.5</v>
+        <v>282</v>
       </c>
       <c r="I102" t="n">
-        <v>53</v>
+        <v>158111.75</v>
       </c>
       <c r="J102" t="n">
-        <v>282</v>
-      </c>
-      <c r="K102" t="n">
-        <v>158111.75</v>
-      </c>
-      <c r="L102" t="n">
         <v>83973</v>
-      </c>
-      <c r="M102" t="n">
-        <v>17788.890625</v>
-      </c>
-      <c r="N102" t="n">
-        <v>17200.109375</v>
-      </c>
-      <c r="O102" t="n">
-        <v>16651.01953125</v>
-      </c>
-      <c r="P102" t="n">
-        <v>21706.6796875</v>
-      </c>
-      <c r="Q102" t="n">
-        <v>73346.69921875</v>
       </c>
     </row>
     <row r="103">
@@ -6306,40 +4150,19 @@
         <v>43148.61731343977</v>
       </c>
       <c r="F103" t="n">
-        <v>26878.75936597504</v>
+        <v>12735.25</v>
       </c>
       <c r="G103" t="n">
-        <v>16269.85794746473</v>
+        <v>52.6175</v>
       </c>
       <c r="H103" t="n">
-        <v>12735.25</v>
+        <v>331.5</v>
       </c>
       <c r="I103" t="n">
-        <v>52.6175</v>
+        <v>155621.75</v>
       </c>
       <c r="J103" t="n">
-        <v>331.5</v>
-      </c>
-      <c r="K103" t="n">
-        <v>155621.75</v>
-      </c>
-      <c r="L103" t="n">
         <v>48853.5</v>
-      </c>
-      <c r="M103" t="n">
-        <v>16269.8603515625</v>
-      </c>
-      <c r="N103" t="n">
-        <v>16335.900390625</v>
-      </c>
-      <c r="O103" t="n">
-        <v>16110.919921875</v>
-      </c>
-      <c r="P103" t="n">
-        <v>16443.419921875</v>
-      </c>
-      <c r="Q103" t="n">
-        <v>65160.1005859375</v>
       </c>
     </row>
     <row r="104">
@@ -6363,40 +4186,19 @@
         <v>21206.97724002375</v>
       </c>
       <c r="F104" t="n">
-        <v>10932.42171048659</v>
+        <v>5633.75</v>
       </c>
       <c r="G104" t="n">
-        <v>10274.55552953715</v>
+        <v>19.3925</v>
       </c>
       <c r="H104" t="n">
-        <v>5633.75</v>
+        <v>163</v>
       </c>
       <c r="I104" t="n">
-        <v>19.3925</v>
+        <v>62336.5</v>
       </c>
       <c r="J104" t="n">
-        <v>163</v>
-      </c>
-      <c r="K104" t="n">
-        <v>62336.5</v>
-      </c>
-      <c r="L104" t="n">
         <v>1810.25</v>
-      </c>
-      <c r="M104" t="n">
-        <v>10274.5595703125</v>
-      </c>
-      <c r="N104" t="n">
-        <v>10309.2001953125</v>
-      </c>
-      <c r="O104" t="n">
-        <v>10243.5400390625</v>
-      </c>
-      <c r="P104" t="n">
-        <v>10132.259765625</v>
-      </c>
-      <c r="Q104" t="n">
-        <v>40959.5595703125</v>
       </c>
     </row>
     <row r="105">
@@ -6420,40 +4222,19 @@
         <v>121996.5075161221</v>
       </c>
       <c r="F105" t="n">
-        <v>65184.10820549953</v>
+        <v>36668.25</v>
       </c>
       <c r="G105" t="n">
-        <v>56812.39931062257</v>
+        <v>106.75</v>
       </c>
       <c r="H105" t="n">
-        <v>36668.25</v>
+        <v>416.25</v>
       </c>
       <c r="I105" t="n">
-        <v>106.75</v>
+        <v>370741</v>
       </c>
       <c r="J105" t="n">
-        <v>416.25</v>
-      </c>
-      <c r="K105" t="n">
-        <v>370741</v>
-      </c>
-      <c r="L105" t="n">
         <v>79175.5</v>
-      </c>
-      <c r="M105" t="n">
-        <v>56812.3984375</v>
-      </c>
-      <c r="N105" t="n">
-        <v>57326.73828125</v>
-      </c>
-      <c r="O105" t="n">
-        <v>57413.9609375</v>
-      </c>
-      <c r="P105" t="n">
-        <v>58435.3984375</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>229988.49609375</v>
       </c>
     </row>
     <row r="106">
@@ -6477,40 +4258,19 @@
         <v>50534.76716098785</v>
       </c>
       <c r="F106" t="n">
-        <v>27185.85684016329</v>
+        <v>13971.5</v>
       </c>
       <c r="G106" t="n">
-        <v>23348.91032082456</v>
+        <v>50.25</v>
       </c>
       <c r="H106" t="n">
-        <v>13971.5</v>
+        <v>195</v>
       </c>
       <c r="I106" t="n">
-        <v>50.25</v>
+        <v>158404.25</v>
       </c>
       <c r="J106" t="n">
-        <v>195</v>
-      </c>
-      <c r="K106" t="n">
-        <v>158404.25</v>
-      </c>
-      <c r="L106" t="n">
         <v>52186</v>
-      </c>
-      <c r="M106" t="n">
-        <v>23348.91015625</v>
-      </c>
-      <c r="N106" t="n">
-        <v>24182.94921875</v>
-      </c>
-      <c r="O106" t="n">
-        <v>24225.240234375</v>
-      </c>
-      <c r="P106" t="n">
-        <v>24049.2890625</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>95806.388671875</v>
       </c>
     </row>
     <row r="107">
@@ -6534,40 +4294,19 @@
         <v>15858.49128871142</v>
       </c>
       <c r="F107" t="n">
-        <v>8814.444895543558</v>
+        <v>3302.75</v>
       </c>
       <c r="G107" t="n">
-        <v>7044.046393167863</v>
+        <v>11.225</v>
       </c>
       <c r="H107" t="n">
-        <v>3302.75</v>
+        <v>112.75</v>
       </c>
       <c r="I107" t="n">
-        <v>11.225</v>
+        <v>40206</v>
       </c>
       <c r="J107" t="n">
-        <v>112.75</v>
-      </c>
-      <c r="K107" t="n">
-        <v>40206</v>
-      </c>
-      <c r="L107" t="n">
         <v>1592</v>
-      </c>
-      <c r="M107" t="n">
-        <v>7044.0498046875</v>
-      </c>
-      <c r="N107" t="n">
-        <v>6899.16015625</v>
-      </c>
-      <c r="O107" t="n">
-        <v>7181.7001953125</v>
-      </c>
-      <c r="P107" t="n">
-        <v>7125.419921875</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>28250.330078125</v>
       </c>
     </row>
     <row r="108">
@@ -6591,40 +4330,19 @@
         <v>5116.043821278654</v>
       </c>
       <c r="F108" t="n">
-        <v>2960.470231648581</v>
+        <v>1510.25</v>
       </c>
       <c r="G108" t="n">
-        <v>2155.573589630073</v>
+        <v>5</v>
       </c>
       <c r="H108" t="n">
-        <v>1510.25</v>
+        <v>72.25</v>
       </c>
       <c r="I108" t="n">
-        <v>5</v>
+        <v>17802</v>
       </c>
       <c r="J108" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="K108" t="n">
-        <v>17802</v>
-      </c>
-      <c r="L108" t="n">
         <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>2155.570068359375</v>
-      </c>
-      <c r="N108" t="n">
-        <v>2096.889892578125</v>
-      </c>
-      <c r="O108" t="n">
-        <v>2013.22998046875</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1932.18994140625</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>8197.8798828125</v>
       </c>
     </row>
     <row r="109">
@@ -6648,40 +4366,19 @@
         <v>17908.63453077368</v>
       </c>
       <c r="F109" t="n">
-        <v>8471.871977035184</v>
+        <v>2828.5</v>
       </c>
       <c r="G109" t="n">
-        <v>9436.762553738501</v>
+        <v>19.6075</v>
       </c>
       <c r="H109" t="n">
-        <v>2828.5</v>
+        <v>276.25</v>
       </c>
       <c r="I109" t="n">
-        <v>19.6075</v>
+        <v>41660</v>
       </c>
       <c r="J109" t="n">
-        <v>276.25</v>
-      </c>
-      <c r="K109" t="n">
-        <v>41660</v>
-      </c>
-      <c r="L109" t="n">
         <v>39286.25</v>
-      </c>
-      <c r="M109" t="n">
-        <v>9436.759765625</v>
-      </c>
-      <c r="N109" t="n">
-        <v>9081.9501953125</v>
-      </c>
-      <c r="O109" t="n">
-        <v>8735.0595703125</v>
-      </c>
-      <c r="P109" t="n">
-        <v>8395.8603515625</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>35649.6298828125</v>
       </c>
     </row>
     <row r="110">
@@ -6705,40 +4402,19 @@
         <v>46430.45649158666</v>
       </c>
       <c r="F110" t="n">
-        <v>26957.4487124715</v>
+        <v>9200.5</v>
       </c>
       <c r="G110" t="n">
-        <v>19473.00777911516</v>
+        <v>85</v>
       </c>
       <c r="H110" t="n">
-        <v>9200.5</v>
+        <v>145</v>
       </c>
       <c r="I110" t="n">
-        <v>85</v>
+        <v>152883.5</v>
       </c>
       <c r="J110" t="n">
-        <v>145</v>
-      </c>
-      <c r="K110" t="n">
-        <v>152883.5</v>
-      </c>
-      <c r="L110" t="n">
         <v>349895.75</v>
-      </c>
-      <c r="M110" t="n">
-        <v>19473.009765625</v>
-      </c>
-      <c r="N110" t="n">
-        <v>22772.880859375</v>
-      </c>
-      <c r="O110" t="n">
-        <v>23299.740234375</v>
-      </c>
-      <c r="P110" t="n">
-        <v>24843.759765625</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>90389.390625</v>
       </c>
     </row>
     <row r="111">
@@ -6762,40 +4438,19 @@
         <v>379906.1815826159</v>
       </c>
       <c r="F111" t="n">
-        <v>205765.1398851927</v>
+        <v>108157.75</v>
       </c>
       <c r="G111" t="n">
-        <v>174141.0416974231</v>
+        <v>388</v>
       </c>
       <c r="H111" t="n">
-        <v>108157.75</v>
+        <v>2104.25</v>
       </c>
       <c r="I111" t="n">
-        <v>388</v>
+        <v>1094993.5</v>
       </c>
       <c r="J111" t="n">
-        <v>2104.25</v>
-      </c>
-      <c r="K111" t="n">
-        <v>1094993.5</v>
-      </c>
-      <c r="L111" t="n">
         <v>663209.5</v>
-      </c>
-      <c r="M111" t="n">
-        <v>174141.046875</v>
-      </c>
-      <c r="N111" t="n">
-        <v>179933.59375</v>
-      </c>
-      <c r="O111" t="n">
-        <v>185632.09375</v>
-      </c>
-      <c r="P111" t="n">
-        <v>190998.40625</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>730705.140625</v>
       </c>
     </row>
     <row r="112">
@@ -6819,40 +4474,19 @@
         <v>39442.70524496723</v>
       </c>
       <c r="F112" t="n">
-        <v>20030.15581522276</v>
+        <v>6829</v>
       </c>
       <c r="G112" t="n">
-        <v>19412.54942974446</v>
+        <v>29.9575</v>
       </c>
       <c r="H112" t="n">
-        <v>6829</v>
+        <v>321.5</v>
       </c>
       <c r="I112" t="n">
-        <v>29.9575</v>
+        <v>91870</v>
       </c>
       <c r="J112" t="n">
-        <v>321.5</v>
-      </c>
-      <c r="K112" t="n">
-        <v>91870</v>
-      </c>
-      <c r="L112" t="n">
         <v>33122.25</v>
-      </c>
-      <c r="M112" t="n">
-        <v>19412.55078125</v>
-      </c>
-      <c r="N112" t="n">
-        <v>19249.150390625</v>
-      </c>
-      <c r="O112" t="n">
-        <v>19333.509765625</v>
-      </c>
-      <c r="P112" t="n">
-        <v>19627.5</v>
-      </c>
-      <c r="Q112" t="n">
-        <v>77622.7109375</v>
       </c>
     </row>
     <row r="113">
@@ -6876,40 +4510,19 @@
         <v>31207.15523738869</v>
       </c>
       <c r="F113" t="n">
-        <v>17755.42609963586</v>
+        <v>7659.75</v>
       </c>
       <c r="G113" t="n">
-        <v>13451.72913775283</v>
+        <v>33.5</v>
       </c>
       <c r="H113" t="n">
-        <v>7659.75</v>
+        <v>167.25</v>
       </c>
       <c r="I113" t="n">
-        <v>33.5</v>
+        <v>104209.5</v>
       </c>
       <c r="J113" t="n">
-        <v>167.25</v>
-      </c>
-      <c r="K113" t="n">
-        <v>104209.5</v>
-      </c>
-      <c r="L113" t="n">
         <v>34150.25</v>
-      </c>
-      <c r="M113" t="n">
-        <v>13451.73046875</v>
-      </c>
-      <c r="N113" t="n">
-        <v>13053.4501953125</v>
-      </c>
-      <c r="O113" t="n">
-        <v>13407.9599609375</v>
-      </c>
-      <c r="P113" t="n">
-        <v>12958.3095703125</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>52871.4501953125</v>
       </c>
     </row>
     <row r="114">
@@ -6933,40 +4546,19 @@
         <v>156897.3297735366</v>
       </c>
       <c r="F114" t="n">
-        <v>83751.65546633513</v>
+        <v>26935</v>
       </c>
       <c r="G114" t="n">
-        <v>73145.67430720148</v>
+        <v>238.925</v>
       </c>
       <c r="H114" t="n">
-        <v>26935</v>
+        <v>990.25</v>
       </c>
       <c r="I114" t="n">
-        <v>238.925</v>
+        <v>326478</v>
       </c>
       <c r="J114" t="n">
-        <v>990.25</v>
-      </c>
-      <c r="K114" t="n">
-        <v>326478</v>
-      </c>
-      <c r="L114" t="n">
         <v>551515.75</v>
-      </c>
-      <c r="M114" t="n">
-        <v>73145.671875</v>
-      </c>
-      <c r="N114" t="n">
-        <v>75524.0390625</v>
-      </c>
-      <c r="O114" t="n">
-        <v>76548.4765625</v>
-      </c>
-      <c r="P114" t="n">
-        <v>77670.6171875</v>
-      </c>
-      <c r="Q114" t="n">
-        <v>302888.8046875</v>
       </c>
     </row>
     <row r="115">
@@ -6990,40 +4582,19 @@
         <v>166856.8884156364</v>
       </c>
       <c r="F115" t="n">
-        <v>91122.05696209548</v>
+        <v>27147.5</v>
       </c>
       <c r="G115" t="n">
-        <v>75734.83145354092</v>
+        <v>199.75</v>
       </c>
       <c r="H115" t="n">
-        <v>27147.5</v>
+        <v>1781.75</v>
       </c>
       <c r="I115" t="n">
-        <v>199.75</v>
+        <v>380557.75</v>
       </c>
       <c r="J115" t="n">
-        <v>1781.75</v>
-      </c>
-      <c r="K115" t="n">
-        <v>380557.75</v>
-      </c>
-      <c r="L115" t="n">
         <v>87003.75</v>
-      </c>
-      <c r="M115" t="n">
-        <v>75734.828125</v>
-      </c>
-      <c r="N115" t="n">
-        <v>76001.3828125</v>
-      </c>
-      <c r="O115" t="n">
-        <v>76895.078125</v>
-      </c>
-      <c r="P115" t="n">
-        <v>77822.078125</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>306453.3671875</v>
       </c>
     </row>
     <row r="116">
@@ -7047,40 +4618,19 @@
         <v>326061.0727683359</v>
       </c>
       <c r="F116" t="n">
-        <v>182036.8822510337</v>
+        <v>63398.25</v>
       </c>
       <c r="G116" t="n">
-        <v>144024.1905173023</v>
+        <v>288.75</v>
       </c>
       <c r="H116" t="n">
-        <v>63398.25</v>
+        <v>1636</v>
       </c>
       <c r="I116" t="n">
-        <v>288.75</v>
+        <v>826099.75</v>
       </c>
       <c r="J116" t="n">
-        <v>1636</v>
-      </c>
-      <c r="K116" t="n">
-        <v>826099.75</v>
-      </c>
-      <c r="L116" t="n">
         <v>612514.75</v>
-      </c>
-      <c r="M116" t="n">
-        <v>144024.1875</v>
-      </c>
-      <c r="N116" t="n">
-        <v>140880.84375</v>
-      </c>
-      <c r="O116" t="n">
-        <v>136704.359375</v>
-      </c>
-      <c r="P116" t="n">
-        <v>138438.625</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>560048.015625</v>
       </c>
     </row>
     <row r="117">
@@ -7104,40 +4654,19 @@
         <v>47955.30529178684</v>
       </c>
       <c r="F117" t="n">
-        <v>25646.41687784491</v>
+        <v>7410.5</v>
       </c>
       <c r="G117" t="n">
-        <v>22308.88841394192</v>
+        <v>54.5</v>
       </c>
       <c r="H117" t="n">
-        <v>7410.5</v>
+        <v>464.5</v>
       </c>
       <c r="I117" t="n">
-        <v>54.5</v>
+        <v>102553.5</v>
       </c>
       <c r="J117" t="n">
-        <v>464.5</v>
-      </c>
-      <c r="K117" t="n">
-        <v>102553.5</v>
-      </c>
-      <c r="L117" t="n">
         <v>197191.75</v>
-      </c>
-      <c r="M117" t="n">
-        <v>22308.890625</v>
-      </c>
-      <c r="N117" t="n">
-        <v>22187.9609375</v>
-      </c>
-      <c r="O117" t="n">
-        <v>22104.0390625</v>
-      </c>
-      <c r="P117" t="n">
-        <v>27329.130859375</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>93930.021484375</v>
       </c>
     </row>
     <row r="118">
@@ -7161,40 +4690,19 @@
         <v>7082.656631682998</v>
       </c>
       <c r="F118" t="n">
-        <v>3938.654996874504</v>
+        <v>700</v>
       </c>
       <c r="G118" t="n">
-        <v>3144.001634808494</v>
+        <v>10</v>
       </c>
       <c r="H118" t="n">
-        <v>700</v>
+        <v>27.5</v>
       </c>
       <c r="I118" t="n">
-        <v>10</v>
+        <v>20937.75</v>
       </c>
       <c r="J118" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="K118" t="n">
-        <v>20937.75</v>
-      </c>
-      <c r="L118" t="n">
         <v>822.75</v>
-      </c>
-      <c r="M118" t="n">
-        <v>3144</v>
-      </c>
-      <c r="N118" t="n">
-        <v>2983.320068359375</v>
-      </c>
-      <c r="O118" t="n">
-        <v>2832.2900390625</v>
-      </c>
-      <c r="P118" t="n">
-        <v>2684.169921875</v>
-      </c>
-      <c r="Q118" t="n">
-        <v>11643.78002929688</v>
       </c>
     </row>
     <row r="119">
@@ -7218,40 +4726,19 @@
         <v>52652.30526642993</v>
       </c>
       <c r="F119" t="n">
-        <v>28312.49734701305</v>
+        <v>14769</v>
       </c>
       <c r="G119" t="n">
-        <v>24339.80791941688</v>
+        <v>47.825</v>
       </c>
       <c r="H119" t="n">
-        <v>14769</v>
+        <v>384.5</v>
       </c>
       <c r="I119" t="n">
-        <v>47.825</v>
+        <v>162685</v>
       </c>
       <c r="J119" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="K119" t="n">
-        <v>162685</v>
-      </c>
-      <c r="L119" t="n">
         <v>47892.25</v>
-      </c>
-      <c r="M119" t="n">
-        <v>24369.919921875</v>
-      </c>
-      <c r="N119" t="n">
-        <v>24340.69921875</v>
-      </c>
-      <c r="O119" t="n">
-        <v>25594.759765625</v>
-      </c>
-      <c r="P119" t="n">
-        <v>27091.619140625</v>
-      </c>
-      <c r="Q119" t="n">
-        <v>101396.998046875</v>
       </c>
     </row>
     <row r="120">
@@ -7275,40 +4762,19 @@
         <v>316537.0727906332</v>
       </c>
       <c r="F120" t="n">
-        <v>168267.1571977919</v>
+        <v>63952</v>
       </c>
       <c r="G120" t="n">
-        <v>148269.9155928413</v>
+        <v>353.5</v>
       </c>
       <c r="H120" t="n">
-        <v>63952</v>
+        <v>4080.5</v>
       </c>
       <c r="I120" t="n">
-        <v>353.5</v>
+        <v>997791.75</v>
       </c>
       <c r="J120" t="n">
-        <v>4080.5</v>
-      </c>
-      <c r="K120" t="n">
-        <v>997791.75</v>
-      </c>
-      <c r="L120" t="n">
         <v>268852</v>
-      </c>
-      <c r="M120" t="n">
-        <v>148267.1875</v>
-      </c>
-      <c r="N120" t="n">
-        <v>152951.234375</v>
-      </c>
-      <c r="O120" t="n">
-        <v>156389.671875</v>
-      </c>
-      <c r="P120" t="n">
-        <v>159259.859375</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>616867.953125</v>
       </c>
     </row>
     <row r="121">
@@ -7332,40 +4798,19 @@
         <v>159171.8899199518</v>
       </c>
       <c r="F121" t="n">
-        <v>94037.53393465647</v>
+        <v>48699.5</v>
       </c>
       <c r="G121" t="n">
-        <v>65134.35598529525</v>
+        <v>150.3</v>
       </c>
       <c r="H121" t="n">
-        <v>48699.5</v>
+        <v>840.75</v>
       </c>
       <c r="I121" t="n">
-        <v>150.3</v>
+        <v>575680.75</v>
       </c>
       <c r="J121" t="n">
-        <v>840.75</v>
-      </c>
-      <c r="K121" t="n">
-        <v>575680.75</v>
-      </c>
-      <c r="L121" t="n">
         <v>110704.25</v>
-      </c>
-      <c r="M121" t="n">
-        <v>65134.359375</v>
-      </c>
-      <c r="N121" t="n">
-        <v>66136.859375</v>
-      </c>
-      <c r="O121" t="n">
-        <v>65782.203125</v>
-      </c>
-      <c r="P121" t="n">
-        <v>65476.30859375</v>
-      </c>
-      <c r="Q121" t="n">
-        <v>262529.73046875</v>
       </c>
     </row>
     <row r="122">
@@ -7389,40 +4834,19 @@
         <v>421649.2177260368</v>
       </c>
       <c r="F122" t="n">
-        <v>231228.4674368631</v>
+        <v>100485</v>
       </c>
       <c r="G122" t="n">
-        <v>190420.7502891736</v>
+        <v>428.5</v>
       </c>
       <c r="H122" t="n">
-        <v>100485</v>
+        <v>2623.25</v>
       </c>
       <c r="I122" t="n">
-        <v>428.5</v>
+        <v>1197326.25</v>
       </c>
       <c r="J122" t="n">
-        <v>2623.25</v>
-      </c>
-      <c r="K122" t="n">
-        <v>1197326.25</v>
-      </c>
-      <c r="L122" t="n">
         <v>589291.25</v>
-      </c>
-      <c r="M122" t="n">
-        <v>190260.6875</v>
-      </c>
-      <c r="N122" t="n">
-        <v>191756.1875</v>
-      </c>
-      <c r="O122" t="n">
-        <v>193137.796875</v>
-      </c>
-      <c r="P122" t="n">
-        <v>194440.234375</v>
-      </c>
-      <c r="Q122" t="n">
-        <v>769594.90625</v>
       </c>
     </row>
     <row r="123">
@@ -7446,40 +4870,19 @@
         <v>36165.95966252762</v>
       </c>
       <c r="F123" t="n">
-        <v>18825.13219163171</v>
+        <v>3995</v>
       </c>
       <c r="G123" t="n">
-        <v>17340.8274708959</v>
+        <v>76.5</v>
       </c>
       <c r="H123" t="n">
-        <v>3995</v>
+        <v>468.25</v>
       </c>
       <c r="I123" t="n">
-        <v>76.5</v>
+        <v>74064.5</v>
       </c>
       <c r="J123" t="n">
-        <v>468.25</v>
-      </c>
-      <c r="K123" t="n">
-        <v>74064.5</v>
-      </c>
-      <c r="L123" t="n">
         <v>23050.5</v>
-      </c>
-      <c r="M123" t="n">
-        <v>17340.830078125</v>
-      </c>
-      <c r="N123" t="n">
-        <v>17894.91015625</v>
-      </c>
-      <c r="O123" t="n">
-        <v>17568.880859375</v>
-      </c>
-      <c r="P123" t="n">
-        <v>17175.73046875</v>
-      </c>
-      <c r="Q123" t="n">
-        <v>69980.3515625</v>
       </c>
     </row>
     <row r="124">
@@ -7503,40 +4906,19 @@
         <v>350473.8304967065</v>
       </c>
       <c r="F124" t="n">
-        <v>197512.8000935437</v>
+        <v>102067.75</v>
       </c>
       <c r="G124" t="n">
-        <v>152961.0304031626</v>
+        <v>370.25</v>
       </c>
       <c r="H124" t="n">
-        <v>102067.75</v>
+        <v>1426.25</v>
       </c>
       <c r="I124" t="n">
-        <v>370.25</v>
+        <v>1089545.25</v>
       </c>
       <c r="J124" t="n">
-        <v>1426.25</v>
-      </c>
-      <c r="K124" t="n">
-        <v>1089545.25</v>
-      </c>
-      <c r="L124" t="n">
         <v>684322.75</v>
-      </c>
-      <c r="M124" t="n">
-        <v>152961.03125</v>
-      </c>
-      <c r="N124" t="n">
-        <v>152351.765625</v>
-      </c>
-      <c r="O124" t="n">
-        <v>155600.109375</v>
-      </c>
-      <c r="P124" t="n">
-        <v>158746.953125</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>619659.859375</v>
       </c>
     </row>
     <row r="125">
@@ -7560,40 +4942,19 @@
         <v>35343.42074993736</v>
       </c>
       <c r="F125" t="n">
-        <v>20740.64036589517</v>
+        <v>8899.5</v>
       </c>
       <c r="G125" t="n">
-        <v>14602.78038404218</v>
+        <v>41.175</v>
       </c>
       <c r="H125" t="n">
-        <v>8899.5</v>
+        <v>207.25</v>
       </c>
       <c r="I125" t="n">
-        <v>41.175</v>
+        <v>106794.75</v>
       </c>
       <c r="J125" t="n">
-        <v>207.25</v>
-      </c>
-      <c r="K125" t="n">
-        <v>106794.75</v>
-      </c>
-      <c r="L125" t="n">
         <v>79050.5</v>
-      </c>
-      <c r="M125" t="n">
-        <v>14602.7802734375</v>
-      </c>
-      <c r="N125" t="n">
-        <v>13800.8603515625</v>
-      </c>
-      <c r="O125" t="n">
-        <v>13009.849609375</v>
-      </c>
-      <c r="P125" t="n">
-        <v>12258.580078125</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>53672.0703125</v>
       </c>
     </row>
     <row r="126">
@@ -7617,40 +4978,19 @@
         <v>39967.18771742355</v>
       </c>
       <c r="F126" t="n">
-        <v>21156.59543835116</v>
+        <v>10407.5</v>
       </c>
       <c r="G126" t="n">
-        <v>18810.59227907239</v>
+        <v>33.23</v>
       </c>
       <c r="H126" t="n">
-        <v>10407.5</v>
+        <v>277.25</v>
       </c>
       <c r="I126" t="n">
-        <v>33.23</v>
+        <v>112082</v>
       </c>
       <c r="J126" t="n">
-        <v>277.25</v>
-      </c>
-      <c r="K126" t="n">
-        <v>112082</v>
-      </c>
-      <c r="L126" t="n">
         <v>45013.75</v>
-      </c>
-      <c r="M126" t="n">
-        <v>18810.58984375</v>
-      </c>
-      <c r="N126" t="n">
-        <v>19864.41015625</v>
-      </c>
-      <c r="O126" t="n">
-        <v>20313.8203125</v>
-      </c>
-      <c r="P126" t="n">
-        <v>20051.19921875</v>
-      </c>
-      <c r="Q126" t="n">
-        <v>79040.01953125</v>
       </c>
     </row>
     <row r="127">
@@ -7674,40 +5014,19 @@
         <v>56268.23593592583</v>
       </c>
       <c r="F127" t="n">
-        <v>32364.00341311267</v>
+        <v>9223.75</v>
       </c>
       <c r="G127" t="n">
-        <v>23904.23252281317</v>
+        <v>37.25</v>
       </c>
       <c r="H127" t="n">
-        <v>9223.75</v>
+        <v>411.25</v>
       </c>
       <c r="I127" t="n">
-        <v>37.25</v>
+        <v>112467.25</v>
       </c>
       <c r="J127" t="n">
-        <v>411.25</v>
-      </c>
-      <c r="K127" t="n">
-        <v>112467.25</v>
-      </c>
-      <c r="L127" t="n">
         <v>39783</v>
-      </c>
-      <c r="M127" t="n">
-        <v>23904.240234375</v>
-      </c>
-      <c r="N127" t="n">
-        <v>25414.259765625</v>
-      </c>
-      <c r="O127" t="n">
-        <v>25408.580078125</v>
-      </c>
-      <c r="P127" t="n">
-        <v>25139.380859375</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>99866.4609375</v>
       </c>
     </row>
     <row r="128">
@@ -7731,40 +5050,19 @@
         <v>61195.04647360237</v>
       </c>
       <c r="F128" t="n">
-        <v>34807.22449139963</v>
+        <v>11914</v>
       </c>
       <c r="G128" t="n">
-        <v>26387.82198220275</v>
+        <v>70.20750000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>11914</v>
+        <v>625.5</v>
       </c>
       <c r="I128" t="n">
-        <v>70.20750000000001</v>
+        <v>159876.25</v>
       </c>
       <c r="J128" t="n">
-        <v>625.5</v>
-      </c>
-      <c r="K128" t="n">
-        <v>159876.25</v>
-      </c>
-      <c r="L128" t="n">
         <v>204197</v>
-      </c>
-      <c r="M128" t="n">
-        <v>26387.8203125</v>
-      </c>
-      <c r="N128" t="n">
-        <v>28321.400390625</v>
-      </c>
-      <c r="O128" t="n">
-        <v>28311.33984375</v>
-      </c>
-      <c r="P128" t="n">
-        <v>27494.5</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>110515.060546875</v>
       </c>
     </row>
     <row r="129">
@@ -7788,40 +5086,19 @@
         <v>276276.3227007691</v>
       </c>
       <c r="F129" t="n">
-        <v>142730.9358235699</v>
+        <v>42872</v>
       </c>
       <c r="G129" t="n">
-        <v>133545.3868771993</v>
+        <v>177.5</v>
       </c>
       <c r="H129" t="n">
-        <v>42872</v>
+        <v>2251</v>
       </c>
       <c r="I129" t="n">
-        <v>177.5</v>
+        <v>533861.5</v>
       </c>
       <c r="J129" t="n">
-        <v>2251</v>
-      </c>
-      <c r="K129" t="n">
-        <v>533861.5</v>
-      </c>
-      <c r="L129" t="n">
         <v>368223.25</v>
-      </c>
-      <c r="M129" t="n">
-        <v>134575.328125</v>
-      </c>
-      <c r="N129" t="n">
-        <v>138740.46875</v>
-      </c>
-      <c r="O129" t="n">
-        <v>144083.765625</v>
-      </c>
-      <c r="P129" t="n">
-        <v>150674.1875</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>568073.75</v>
       </c>
     </row>
     <row r="130">
@@ -7845,40 +5122,19 @@
         <v>21954.96837450299</v>
       </c>
       <c r="F130" t="n">
-        <v>12193.46075943609</v>
+        <v>4960.5</v>
       </c>
       <c r="G130" t="n">
-        <v>9761.507615066899</v>
+        <v>22.5</v>
       </c>
       <c r="H130" t="n">
-        <v>4960.5</v>
+        <v>112.25</v>
       </c>
       <c r="I130" t="n">
-        <v>22.5</v>
+        <v>63228.5</v>
       </c>
       <c r="J130" t="n">
-        <v>112.25</v>
-      </c>
-      <c r="K130" t="n">
-        <v>63228.5</v>
-      </c>
-      <c r="L130" t="n">
         <v>53722</v>
-      </c>
-      <c r="M130" t="n">
-        <v>9761.509765625</v>
-      </c>
-      <c r="N130" t="n">
-        <v>9278.2099609375</v>
-      </c>
-      <c r="O130" t="n">
-        <v>8808.8603515625</v>
-      </c>
-      <c r="P130" t="n">
-        <v>8343.240234375</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>36191.8203125</v>
       </c>
     </row>
     <row r="131">
@@ -7902,40 +5158,19 @@
         <v>5506.174681735101</v>
       </c>
       <c r="F131" t="n">
-        <v>3922.446001913082</v>
+        <v>1840.25</v>
       </c>
       <c r="G131" t="n">
-        <v>1583.72867982202</v>
+        <v>7</v>
       </c>
       <c r="H131" t="n">
-        <v>1840.25</v>
+        <v>100</v>
       </c>
       <c r="I131" t="n">
-        <v>7</v>
+        <v>23912</v>
       </c>
       <c r="J131" t="n">
-        <v>100</v>
-      </c>
-      <c r="K131" t="n">
-        <v>23912</v>
-      </c>
-      <c r="L131" t="n">
         <v>710.25</v>
-      </c>
-      <c r="M131" t="n">
-        <v>1583.72998046875</v>
-      </c>
-      <c r="N131" t="n">
-        <v>1436.010009765625</v>
-      </c>
-      <c r="O131" t="n">
-        <v>1309.93994140625</v>
-      </c>
-      <c r="P131" t="n">
-        <v>1195.380004882812</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>5525.059936523438</v>
       </c>
     </row>
     <row r="132">
@@ -7959,40 +5194,19 @@
         <v>20.1739467461</v>
       </c>
       <c r="F132" t="n">
-        <v>13.85179103224778</v>
+        <v>7</v>
       </c>
       <c r="G132" t="n">
-        <v>6.322155713852222</v>
+        <v>0.08</v>
       </c>
       <c r="H132" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0.08</v>
+        <v>107</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>107</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>6.320000171661377</v>
-      </c>
-      <c r="N132" t="n">
-        <v>5.690000057220459</v>
-      </c>
-      <c r="O132" t="n">
-        <v>5.070000171661377</v>
-      </c>
-      <c r="P132" t="n">
-        <v>4.440000057220459</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>21.52000045776367</v>
       </c>
     </row>
     <row r="133">
@@ -8016,40 +5230,19 @@
         <v>77134.67426409999</v>
       </c>
       <c r="F133" t="n">
-        <v>43992.46209170438</v>
+        <v>21270.5</v>
       </c>
       <c r="G133" t="n">
-        <v>33142.21217239561</v>
+        <v>80</v>
       </c>
       <c r="H133" t="n">
-        <v>21270.5</v>
+        <v>584.25</v>
       </c>
       <c r="I133" t="n">
-        <v>80</v>
+        <v>238713.75</v>
       </c>
       <c r="J133" t="n">
-        <v>584.25</v>
-      </c>
-      <c r="K133" t="n">
-        <v>238713.75</v>
-      </c>
-      <c r="L133" t="n">
         <v>112829.25</v>
-      </c>
-      <c r="M133" t="n">
-        <v>33142.2109375</v>
-      </c>
-      <c r="N133" t="n">
-        <v>33079.6015625</v>
-      </c>
-      <c r="O133" t="n">
-        <v>32381.380859375</v>
-      </c>
-      <c r="P133" t="n">
-        <v>32140.689453125</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>130743.8828125</v>
       </c>
     </row>
     <row r="134">
@@ -8073,40 +5266,19 @@
         <v>29438.05499330461</v>
       </c>
       <c r="F134" t="n">
-        <v>15967.65219481112</v>
+        <v>4629</v>
       </c>
       <c r="G134" t="n">
-        <v>13470.40279849349</v>
+        <v>22</v>
       </c>
       <c r="H134" t="n">
-        <v>4629</v>
+        <v>300.25</v>
       </c>
       <c r="I134" t="n">
-        <v>22</v>
+        <v>63784.25</v>
       </c>
       <c r="J134" t="n">
-        <v>300.25</v>
-      </c>
-      <c r="K134" t="n">
-        <v>63784.25</v>
-      </c>
-      <c r="L134" t="n">
         <v>29514</v>
-      </c>
-      <c r="M134" t="n">
-        <v>13470.400390625</v>
-      </c>
-      <c r="N134" t="n">
-        <v>13143.7001953125</v>
-      </c>
-      <c r="O134" t="n">
-        <v>12850.7802734375</v>
-      </c>
-      <c r="P134" t="n">
-        <v>12561.7001953125</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>52026.5810546875</v>
       </c>
     </row>
     <row r="135">
@@ -8130,40 +5302,19 @@
         <v>171942.5795231811</v>
       </c>
       <c r="F135" t="n">
-        <v>91542.88288499243</v>
+        <v>33931.5</v>
       </c>
       <c r="G135" t="n">
-        <v>80399.69663818865</v>
+        <v>133.25</v>
       </c>
       <c r="H135" t="n">
-        <v>33931.5</v>
+        <v>1319.75</v>
       </c>
       <c r="I135" t="n">
-        <v>133.25</v>
+        <v>445455.25</v>
       </c>
       <c r="J135" t="n">
-        <v>1319.75</v>
-      </c>
-      <c r="K135" t="n">
-        <v>445455.25</v>
-      </c>
-      <c r="L135" t="n">
         <v>111806.75</v>
-      </c>
-      <c r="M135" t="n">
-        <v>80398.96875</v>
-      </c>
-      <c r="N135" t="n">
-        <v>81084.5390625</v>
-      </c>
-      <c r="O135" t="n">
-        <v>81748.359375</v>
-      </c>
-      <c r="P135" t="n">
-        <v>82368.21875</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>325600.0859375</v>
       </c>
     </row>
     <row r="136">
@@ -8187,40 +5338,19 @@
         <v>170514.4901754355</v>
       </c>
       <c r="F136" t="n">
-        <v>94374.67369698625</v>
+        <v>33519</v>
       </c>
       <c r="G136" t="n">
-        <v>76139.81647844923</v>
+        <v>109.235</v>
       </c>
       <c r="H136" t="n">
-        <v>33519</v>
+        <v>981.25</v>
       </c>
       <c r="I136" t="n">
-        <v>109.235</v>
+        <v>418802.75</v>
       </c>
       <c r="J136" t="n">
-        <v>981.25</v>
-      </c>
-      <c r="K136" t="n">
-        <v>418802.75</v>
-      </c>
-      <c r="L136" t="n">
         <v>110009.25</v>
-      </c>
-      <c r="M136" t="n">
-        <v>76139.8125</v>
-      </c>
-      <c r="N136" t="n">
-        <v>75332.8125</v>
-      </c>
-      <c r="O136" t="n">
-        <v>74541.421875</v>
-      </c>
-      <c r="P136" t="n">
-        <v>73784.7421875</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>299798.7890625</v>
       </c>
     </row>
     <row r="137">
@@ -8244,40 +5374,19 @@
         <v>30381.60922771465</v>
       </c>
       <c r="F137" t="n">
-        <v>15535.218009176</v>
+        <v>4198.25</v>
       </c>
       <c r="G137" t="n">
-        <v>14846.39121853864</v>
+        <v>43.1</v>
       </c>
       <c r="H137" t="n">
-        <v>4198.25</v>
+        <v>291.5</v>
       </c>
       <c r="I137" t="n">
-        <v>43.1</v>
+        <v>60756.5</v>
       </c>
       <c r="J137" t="n">
-        <v>291.5</v>
-      </c>
-      <c r="K137" t="n">
-        <v>60756.5</v>
-      </c>
-      <c r="L137" t="n">
         <v>156058.25</v>
-      </c>
-      <c r="M137" t="n">
-        <v>14846.3896484375</v>
-      </c>
-      <c r="N137" t="n">
-        <v>14698.3603515625</v>
-      </c>
-      <c r="O137" t="n">
-        <v>14627.33984375</v>
-      </c>
-      <c r="P137" t="n">
-        <v>16701.5703125</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>60873.66015625</v>
       </c>
     </row>
     <row r="138">
@@ -8301,40 +5410,19 @@
         <v>71674.78145284049</v>
       </c>
       <c r="F138" t="n">
-        <v>35418.47005081534</v>
+        <v>17306.5</v>
       </c>
       <c r="G138" t="n">
-        <v>36256.31140202515</v>
+        <v>71.75</v>
       </c>
       <c r="H138" t="n">
-        <v>17306.5</v>
+        <v>188.25</v>
       </c>
       <c r="I138" t="n">
-        <v>71.75</v>
+        <v>219086</v>
       </c>
       <c r="J138" t="n">
-        <v>188.25</v>
-      </c>
-      <c r="K138" t="n">
-        <v>219086</v>
-      </c>
-      <c r="L138" t="n">
         <v>59515</v>
-      </c>
-      <c r="M138" t="n">
-        <v>36258.01953125</v>
-      </c>
-      <c r="N138" t="n">
-        <v>35378.12890625</v>
-      </c>
-      <c r="O138" t="n">
-        <v>34500.73828125</v>
-      </c>
-      <c r="P138" t="n">
-        <v>33608.94140625</v>
-      </c>
-      <c r="Q138" t="n">
-        <v>139745.828125</v>
       </c>
     </row>
     <row r="139">
@@ -8358,40 +5446,19 @@
         <v>4832331.880195849</v>
       </c>
       <c r="F139" t="n">
-        <v>2521830.189683721</v>
+        <v>1035833.25</v>
       </c>
       <c r="G139" t="n">
-        <v>2310501.690512128</v>
+        <v>4870.6875</v>
       </c>
       <c r="H139" t="n">
-        <v>1035833.25</v>
+        <v>46038.75</v>
       </c>
       <c r="I139" t="n">
-        <v>4870.6875</v>
+        <v>13409449.5</v>
       </c>
       <c r="J139" t="n">
-        <v>46038.75</v>
-      </c>
-      <c r="K139" t="n">
-        <v>13409449.5</v>
-      </c>
-      <c r="L139" t="n">
         <v>3905286</v>
-      </c>
-      <c r="M139" t="n">
-        <v>2310501.75</v>
-      </c>
-      <c r="N139" t="n">
-        <v>2302721</v>
-      </c>
-      <c r="O139" t="n">
-        <v>2293893.75</v>
-      </c>
-      <c r="P139" t="n">
-        <v>2282826</v>
-      </c>
-      <c r="Q139" t="n">
-        <v>9189942.5</v>
       </c>
     </row>
     <row r="140">
@@ -8415,40 +5482,19 @@
         <v>4379939.023763056</v>
       </c>
       <c r="F140" t="n">
-        <v>2209774.717774209</v>
+        <v>896386.5</v>
       </c>
       <c r="G140" t="n">
-        <v>2170164.305988849</v>
+        <v>3819.5</v>
       </c>
       <c r="H140" t="n">
-        <v>896386.5</v>
+        <v>42611</v>
       </c>
       <c r="I140" t="n">
-        <v>3819.5</v>
+        <v>10936351.25</v>
       </c>
       <c r="J140" t="n">
-        <v>42611</v>
-      </c>
-      <c r="K140" t="n">
-        <v>10936351.25</v>
-      </c>
-      <c r="L140" t="n">
         <v>2828429</v>
-      </c>
-      <c r="M140" t="n">
-        <v>2170071.5</v>
-      </c>
-      <c r="N140" t="n">
-        <v>2213340.5</v>
-      </c>
-      <c r="O140" t="n">
-        <v>2255853</v>
-      </c>
-      <c r="P140" t="n">
-        <v>2294015</v>
-      </c>
-      <c r="Q140" t="n">
-        <v>8933280</v>
       </c>
     </row>
     <row r="141">
@@ -8472,40 +5518,19 @@
         <v>3530396.942196433</v>
       </c>
       <c r="F141" t="n">
-        <v>1804774.786165886</v>
+        <v>968386.25</v>
       </c>
       <c r="G141" t="n">
-        <v>1725622.156030549</v>
+        <v>3518.29</v>
       </c>
       <c r="H141" t="n">
-        <v>968386.25</v>
+        <v>24455.25</v>
       </c>
       <c r="I141" t="n">
-        <v>3518.29</v>
+        <v>10863817.5</v>
       </c>
       <c r="J141" t="n">
-        <v>24455.25</v>
-      </c>
-      <c r="K141" t="n">
-        <v>10863817.5</v>
-      </c>
-      <c r="L141" t="n">
         <v>3635858</v>
-      </c>
-      <c r="M141" t="n">
-        <v>1725622.25</v>
-      </c>
-      <c r="N141" t="n">
-        <v>1713772.125</v>
-      </c>
-      <c r="O141" t="n">
-        <v>1735893.125</v>
-      </c>
-      <c r="P141" t="n">
-        <v>1783465</v>
-      </c>
-      <c r="Q141" t="n">
-        <v>6958752.5</v>
       </c>
     </row>
     <row r="142">
@@ -8529,40 +5554,19 @@
         <v>98416.65740489957</v>
       </c>
       <c r="F142" t="n">
-        <v>54106.80738624559</v>
+        <v>23082</v>
       </c>
       <c r="G142" t="n">
-        <v>44309.85001865398</v>
+        <v>93.5</v>
       </c>
       <c r="H142" t="n">
-        <v>23082</v>
+        <v>856</v>
       </c>
       <c r="I142" t="n">
-        <v>93.5</v>
+        <v>256139.75</v>
       </c>
       <c r="J142" t="n">
-        <v>856</v>
-      </c>
-      <c r="K142" t="n">
-        <v>256139.75</v>
-      </c>
-      <c r="L142" t="n">
         <v>190179</v>
-      </c>
-      <c r="M142" t="n">
-        <v>44016.12109375</v>
-      </c>
-      <c r="N142" t="n">
-        <v>45206.7109375</v>
-      </c>
-      <c r="O142" t="n">
-        <v>49203.19921875</v>
-      </c>
-      <c r="P142" t="n">
-        <v>58895.73828125</v>
-      </c>
-      <c r="Q142" t="n">
-        <v>197321.76953125</v>
       </c>
     </row>
     <row r="143">
@@ -8586,40 +5590,19 @@
         <v>12752.48982424101</v>
       </c>
       <c r="F143" t="n">
-        <v>7506.69949826322</v>
+        <v>3602.75</v>
       </c>
       <c r="G143" t="n">
-        <v>5245.790325977788</v>
+        <v>13.65</v>
       </c>
       <c r="H143" t="n">
-        <v>3602.75</v>
+        <v>63.75</v>
       </c>
       <c r="I143" t="n">
-        <v>13.65</v>
+        <v>43089.5</v>
       </c>
       <c r="J143" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="K143" t="n">
-        <v>43089.5</v>
-      </c>
-      <c r="L143" t="n">
         <v>12380.75</v>
-      </c>
-      <c r="M143" t="n">
-        <v>5245.64013671875</v>
-      </c>
-      <c r="N143" t="n">
-        <v>5387.06982421875</v>
-      </c>
-      <c r="O143" t="n">
-        <v>5392.85986328125</v>
-      </c>
-      <c r="P143" t="n">
-        <v>5453.7099609375</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>21479.27978515625</v>
       </c>
     </row>
     <row r="144">
@@ -8643,40 +5626,19 @@
         <v>22460.81713727744</v>
       </c>
       <c r="F144" t="n">
-        <v>12814.41329204355</v>
+        <v>7525.5</v>
       </c>
       <c r="G144" t="n">
-        <v>9646.40384523389</v>
+        <v>36</v>
       </c>
       <c r="H144" t="n">
-        <v>7525.5</v>
+        <v>159.5</v>
       </c>
       <c r="I144" t="n">
-        <v>36</v>
+        <v>93072</v>
       </c>
       <c r="J144" t="n">
-        <v>159.5</v>
-      </c>
-      <c r="K144" t="n">
-        <v>93072</v>
-      </c>
-      <c r="L144" t="n">
         <v>62436.25</v>
-      </c>
-      <c r="M144" t="n">
-        <v>9683.2998046875</v>
-      </c>
-      <c r="N144" t="n">
-        <v>9753.76953125</v>
-      </c>
-      <c r="O144" t="n">
-        <v>9679.8798828125</v>
-      </c>
-      <c r="P144" t="n">
-        <v>9817.759765625</v>
-      </c>
-      <c r="Q144" t="n">
-        <v>38934.708984375</v>
       </c>
     </row>
     <row r="145">
@@ -8700,40 +5662,19 @@
         <v>16738.4419627772</v>
       </c>
       <c r="F145" t="n">
-        <v>9626.910053540321</v>
+        <v>4023.5</v>
       </c>
       <c r="G145" t="n">
-        <v>7111.531909236882</v>
+        <v>16.225</v>
       </c>
       <c r="H145" t="n">
-        <v>4023.5</v>
+        <v>122.25</v>
       </c>
       <c r="I145" t="n">
-        <v>16.225</v>
+        <v>54111.75</v>
       </c>
       <c r="J145" t="n">
-        <v>122.25</v>
-      </c>
-      <c r="K145" t="n">
-        <v>54111.75</v>
-      </c>
-      <c r="L145" t="n">
         <v>9389.5</v>
-      </c>
-      <c r="M145" t="n">
-        <v>7111.52978515625</v>
-      </c>
-      <c r="N145" t="n">
-        <v>7029.919921875</v>
-      </c>
-      <c r="O145" t="n">
-        <v>6971.7001953125</v>
-      </c>
-      <c r="P145" t="n">
-        <v>7081.18017578125</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>28194.330078125</v>
       </c>
     </row>
     <row r="146">
@@ -8757,40 +5698,19 @@
         <v>47365.22316117388</v>
       </c>
       <c r="F146" t="n">
-        <v>22364.29727519086</v>
+        <v>8915.25</v>
       </c>
       <c r="G146" t="n">
-        <v>25000.92588598303</v>
+        <v>47.64999999999999</v>
       </c>
       <c r="H146" t="n">
-        <v>8915.25</v>
+        <v>311.5</v>
       </c>
       <c r="I146" t="n">
-        <v>47.64999999999999</v>
+        <v>124383</v>
       </c>
       <c r="J146" t="n">
-        <v>311.5</v>
-      </c>
-      <c r="K146" t="n">
-        <v>124383</v>
-      </c>
-      <c r="L146" t="n">
         <v>66916</v>
-      </c>
-      <c r="M146" t="n">
-        <v>25000.919921875</v>
-      </c>
-      <c r="N146" t="n">
-        <v>25011.30078125</v>
-      </c>
-      <c r="O146" t="n">
-        <v>25158.05078125</v>
-      </c>
-      <c r="P146" t="n">
-        <v>25167.580078125</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>100337.8515625</v>
       </c>
     </row>
     <row r="147">
@@ -8814,40 +5734,19 @@
         <v>22515.29076908376</v>
       </c>
       <c r="F147" t="n">
-        <v>12735.50040059092</v>
+        <v>8249</v>
       </c>
       <c r="G147" t="n">
-        <v>9779.790368492841</v>
+        <v>24.625</v>
       </c>
       <c r="H147" t="n">
-        <v>8249</v>
+        <v>92.25</v>
       </c>
       <c r="I147" t="n">
-        <v>24.625</v>
+        <v>87047</v>
       </c>
       <c r="J147" t="n">
-        <v>92.25</v>
-      </c>
-      <c r="K147" t="n">
-        <v>87047</v>
-      </c>
-      <c r="L147" t="n">
         <v>15244</v>
-      </c>
-      <c r="M147" t="n">
-        <v>9736.2998046875</v>
-      </c>
-      <c r="N147" t="n">
-        <v>10293.73046875</v>
-      </c>
-      <c r="O147" t="n">
-        <v>10725.5</v>
-      </c>
-      <c r="P147" t="n">
-        <v>11346.8798828125</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>42102.41015625</v>
       </c>
     </row>
     <row r="148">
@@ -8871,40 +5770,19 @@
         <v>53264.00181656522</v>
       </c>
       <c r="F148" t="n">
-        <v>29539.08314782992</v>
+        <v>14945</v>
       </c>
       <c r="G148" t="n">
-        <v>23724.9186687353</v>
+        <v>53.2675</v>
       </c>
       <c r="H148" t="n">
-        <v>14945</v>
+        <v>236.75</v>
       </c>
       <c r="I148" t="n">
-        <v>53.2675</v>
+        <v>179313.5</v>
       </c>
       <c r="J148" t="n">
-        <v>236.75</v>
-      </c>
-      <c r="K148" t="n">
-        <v>179313.5</v>
-      </c>
-      <c r="L148" t="n">
         <v>33074.5</v>
-      </c>
-      <c r="M148" t="n">
-        <v>23724.919921875</v>
-      </c>
-      <c r="N148" t="n">
-        <v>24466.0390625</v>
-      </c>
-      <c r="O148" t="n">
-        <v>25112.380859375</v>
-      </c>
-      <c r="P148" t="n">
-        <v>25636.869140625</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>98940.208984375</v>
       </c>
     </row>
     <row r="149">
@@ -8928,40 +5806,19 @@
         <v>855.6873680764546</v>
       </c>
       <c r="F149" t="n">
-        <v>514.1746830806785</v>
+        <v>277.25</v>
       </c>
       <c r="G149" t="n">
-        <v>341.5126849957761</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>277.25</v>
+        <v>15</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>2627.75</v>
       </c>
       <c r="J149" t="n">
-        <v>15</v>
-      </c>
-      <c r="K149" t="n">
-        <v>2627.75</v>
-      </c>
-      <c r="L149" t="n">
         <v>0</v>
-      </c>
-      <c r="M149" t="n">
-        <v>341.510009765625</v>
-      </c>
-      <c r="N149" t="n">
-        <v>325.4500122070312</v>
-      </c>
-      <c r="O149" t="n">
-        <v>312.6600036621094</v>
-      </c>
-      <c r="P149" t="n">
-        <v>297.1700134277344</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>1276.7900390625</v>
       </c>
     </row>
   </sheetData>
